--- a/research/dataset/TierA_paper_table.xlsx
+++ b/research/dataset/TierA_paper_table.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH232"/>
+  <dimension ref="A1:AH234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30053,7 +30053,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TRANSLUCE-2024-10-JAI1</t>
+          <t>TRANSLUCE-2024-10-JAI1-s1</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -30088,7 +30088,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Llama-3.1 8B, Llama-3.1 405B, GPT-4o, GPT-4o-mini, Claude 3.5 Sonnet</t>
+          <t>Llama-3.1 405B (Meta); investigator agents trained on Llama-3.1 8B (Meta)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -30103,12 +30103,12 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Transluce found investigator agents trained on Llama-3.1 8B achieved a 95.5% attack success rate against Llama-3.1 405B, with attacks transferring to proprietary models -- 65.8% against GPT-4o and 22.6% against Claude 3.5 Sonnet.</t>
+          <t>Transluce found investigator agents trained on Llama-3.1 8B achieved a 95.5% attack success rate against Meta's Llama-3.1 405B.</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>we achieve a 95.5% attack success rate against Llama-3.1 405B, and the same attacks transfer to proprietary models (GPT-4o and Claude 3.5 Sonnet), with up to 65.8% success rate against GPT-4o.; Claude 3.5 Sonnet | 22.6%</t>
+          <t>we achieve a 95.5% attack success rate against Llama-3.1 405B</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -30185,32 +30185,32 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SCALEAI-2024-10-JAI1</t>
+          <t>TRANSLUCE-2024-10-JAI1-s2</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SCALEAI-2024-10</t>
+          <t>TRANSLUCE-2024-10</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Transluce</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>For-Profit</t>
+          <t>Non-Profit (AIEF)</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Refusal-Trained LLMs Are Easily Jailbroken As Browser Agents</t>
+          <t>Eliciting Language Model Behaviors with Investigator Agents</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -30220,7 +30220,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>GPT-4o; o1-preview</t>
+          <t>GPT-4o (OpenAI)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -30230,72 +30230,36 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://static.scale.com/uploads/6691558a94899f2f65a87a75/_ICLR__Red_Teaming_Browser_Agents%20(14).pdf</t>
+          <t>https://transluce.org/automated-elicitation</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>With human rewrites of the 100 BrowserART harmful behaviours, browser agents built on GPT-4o and o1-preview pursued 98 and 63 of the 100 harmful behaviours respectively, despite the same backbone models refusing the equivalent requests in chat.</t>
+          <t>Transluce found the investigator-agent attacks developed against Llama-3.1 405B transferred to OpenAI's GPT-4o, with up to a 65.8% attack success rate.</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>With human rewrites, GPT-4o and o1-preview -based browser agents pursued 98 and 63 harmful behaviors (out of 100), respectively.</t>
-        </is>
-      </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="O207" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="P207" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
+          <t>the same attacks transfer to proprietary models (GPT-4o and Claude 3.5 Sonnet), with up to 65.8% success rate against GPT-4o.</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>No explicit attribution</t>
-        </is>
-      </c>
-      <c r="R207" t="inlineStr">
-        <is>
-          <t>OpenAI deployed its GPT-4o-based Operator browser agent with proactive refusals for harmful tasks, confirmation prompts before critical actions, monitoring, and complete restrictions on some high-risk activities.</t>
-        </is>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>To address these risks, we have implemented a multi-layered approach to safety, including proactive refusals of high-risk tasks, confirmation prompts before critical actions, and active monitoring systems to detect and mitigate potential threats.</t>
-        </is>
-      </c>
-      <c r="T207" t="inlineStr">
-        <is>
-          <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="U207" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>https://openai.com/index/operator-system-card/</t>
-        </is>
-      </c>
+          <t>No response located</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr"/>
+      <c r="S207" t="inlineStr"/>
+      <c r="T207" t="inlineStr"/>
+      <c r="U207" t="inlineStr"/>
+      <c r="V207" t="inlineStr"/>
       <c r="W207" t="inlineStr">
         <is>
-          <t>Substantive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="X207" t="inlineStr">
@@ -30313,16 +30277,12 @@
       <c r="AB207" t="inlineStr"/>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>Google Scholar: 38 citations: https://scholar.google.com/scholar?hl=en&amp;as_sdt=0%2C5&amp;q=%22Refusal-Trained%20LLMs%20Are%20Easily%20Jailbroken%20As%20Browser%20Agents%22</t>
+          <t>Chowdhury, Schwettmann, Steinhardt, "Automatically Jailbreaking Frontier Language Models with Investigator Agents" (Transluce, 2025) -- 6 citations per Google Scholar, accessed 2026-08-02</t>
         </is>
       </c>
       <c r="AD207" t="inlineStr"/>
       <c r="AE207" t="inlineStr"/>
-      <c r="AF207" t="inlineStr">
-        <is>
-          <t>Proportionate</t>
-        </is>
-      </c>
+      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="inlineStr">
         <is>
           <t>capability-finding</t>
@@ -30337,32 +30297,32 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SCALEAI-2024-10-JAI5</t>
+          <t>TRANSLUCE-2024-10-JAI1-s3</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SCALEAI-2024-10</t>
+          <t>TRANSLUCE-2024-10</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Transluce</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>For-Profit</t>
+          <t>Non-Profit (AIEF)</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Refusal-Trained LLMs Are Easily Jailbroken As Browser Agents</t>
+          <t>Eliciting Language Model Behaviors with Investigator Agents</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -30372,7 +30332,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>GPT-4o, o1-preview (as browser agents)</t>
+          <t>Claude 3.5 Sonnet (Anthropic)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -30382,39 +30342,23 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>https://static.scale.com/uploads/6691558a94899f2f65a87a75/_ICLR__Red_Teaming_Browser_Agents%20(14).pdf</t>
+          <t>https://transluce.org/automated-elicitation</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Scale AI's red team found that refusal training does not transfer from chat to browser-agent contexts: with human rewrites, GPT-4o and o1-preview based browser agents pursued 98 and 63 of 100 harmful behaviours respectively, even though the same backbone LLMs refuse those instructions as chatbots.</t>
+          <t>Transluce found the investigator-agent attacks developed against Llama-3.1 405B transferred to Anthropic's Claude 3.5 Sonnet, with a 22.6% attack success rate.</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>With human rewrites, GPT-4o and o1-preview -based browser agents pursued 98 and 63 harmful behaviors (out of 100), respectively.</t>
-        </is>
-      </c>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="O208" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="P208" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
+          <t>the same attacks transfer to proprietary models (GPT-4o and Claude 3.5 Sonnet)...; Claude 3.5 Sonnet | 22.6%</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
       <c r="Q208" t="inlineStr">
         <is>
           <t>No response located</t>
@@ -30445,20 +30389,12 @@
       <c r="AB208" t="inlineStr"/>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>Semantic Scholar Graph API, paperId 73bb64ec0f1541e58e668845334f14c58d5f79a6, 'Refusal-Trained LLMs Are Easily Jailbroken As Browser Agents', arXiv:2410.13886, publicationDate 2024-10-11, venue arXiv.org: citationCount 67, influentialCitationCount 3 (retrieved 2026-08-29 from https://api.semanticscholar.org/graph/v1/paper/arXiv:2410.13886).</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>None located</t>
-        </is>
-      </c>
+          <t>Chowdhury, Schwettmann, Steinhardt, "Automatically Jailbreaking Frontier Language Models with Investigator Agents" (Transluce, 2025) -- 6 citations per Google Scholar, accessed 2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr"/>
       <c r="AE208" t="inlineStr"/>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>Accountability gap (no action)</t>
-        </is>
-      </c>
+      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="inlineStr">
         <is>
           <t>capability-finding</t>
@@ -30473,27 +30409,27 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>UKAISI-2024-10-JAI1</t>
+          <t>SCALEAI-2024-10-JAI1</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>UKAISI-2024-10</t>
+          <t>SCALEAI-2024-10</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>UK AISI</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>For-Profit</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AgentHarm: A Benchmark for Measuring Harmfulness of LLM Agents</t>
+          <t>Refusal-Trained LLMs Are Easily Jailbroken As Browser Agents</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -30508,7 +30444,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Mistral Large 2</t>
+          <t>GPT-4o; o1-preview</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -30518,17 +30454,17 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2410.09024</t>
+          <t>https://static.scale.com/uploads/6691558a94899f2f65a87a75/_ICLR__Red_Teaming_Browser_Agents%20(14).pdf</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Some leading LLMs comply with malicious agentic requests at high rates without any jailbreaking — worst case Mistral Large 2 refused only 1.1% of requests and scored 82.2% harm — suggesting agents may be less robust than chatbots against misuse.</t>
+          <t>With human rewrites of the 100 BrowserART harmful behaviours, browser agents built on GPT-4o and o1-preview pursued 98 and 63 of the 100 harmful behaviours respectively, despite the same backbone models refusing the equivalent requests in chat.</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>Mistral Large 2 refuses just 1.1% of requests and gets our strongest score without attacking of 82.2%.</t>
+          <t>With human rewrites, GPT-4o and o1-preview -based browser agents pursued 98 and 63 harmful behaviors (out of 100), respectively.</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -30553,54 +30489,62 @@
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>No response located</t>
-        </is>
-      </c>
-      <c r="R209" t="inlineStr"/>
-      <c r="S209" t="inlineStr"/>
-      <c r="T209" t="inlineStr"/>
-      <c r="U209" t="inlineStr"/>
-      <c r="V209" t="inlineStr"/>
+          <t>No explicit attribution</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>OpenAI deployed its GPT-4o-based Operator browser agent with proactive refusals for harmful tasks, confirmation prompts before critical actions, monitoring, and complete restrictions on some high-risk activities.</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>To address these risks, we have implemented a multi-layered approach to safety, including proactive refusals of high-risk tasks, confirmation prompts before critical actions, and active monitoring systems to detect and mitigate potential threats.</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>https://openai.com/index/operator-system-card/</t>
+        </is>
+      </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Substantive</t>
         </is>
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>Non-binding policy-related uptake</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>NIST named the AgentHarm report in NIST AI 100-2e2025, "Adversarial Machine Learning: A Taxonomy and Terminology of Attacks and Mitigations" (US Department of Commerce / NIST, March 2025), citing it in Sec. 3.5 as emerging research evaluating the vulnerability of LLM agents to AML attacks and naming it in Sec. 3.6 among the benchmarks for evaluating models' susceptibility to jailbreaks, with a full bibliographic citation at reference [12]. Official US federal agency engagement with the report; the publication is a voluntary taxonomy and imposes no enforceable obligation.</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>NIST AI 100-2e2025, Sec. 3.6 (Benchmarks for AML Vulnerabilities): "Datasets like JailbreakBench [72], AdvBench [448], HarmBench [237], StrongREJECT [351], AgentHarm [12], and Do-Not-Answer [399] provide benchmarks for evaluating models' susceptibility to jailbreaks." || Sec. 3.5 (Security of Agents): "Security research focused specifically on agents is still in its early stages, but researchers have begun to evaluate the vulnerability of agents to particular AML attacks [12, 430] and to propose interventions to manage the security risks posed by agents [24]." || Reference [12]: "Maksym Andriushchenko, Alexandra Souly, Mateusz Dziemian, Derek Duenas, Maxwell Lin, Justin Wang, Dan Hendrycks, Andy Zou, Zico Kolter, Matt Fredrikson, Eric Winsor, Jerome Wynne, Yarin Gal, and Xander Davies. Agentharm: A benchmark for measuring harmfulness of llm agents, 2024. URL: https://arxiv.org/abs/2410.09024, arXiv:2410.09024."</t>
-        </is>
-      </c>
+          <t>No policy uptake identified</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr"/>
+      <c r="Z209" t="inlineStr"/>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-2e2025.pdf</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>AZoAI (https://www.azoai.com/news/20241016/AgentHarm-Benchmark-Exposes-Weaknesses-in-AI-Agents-to-Harmful-Misuse-and-Jailbreaking.aspx); MarkTechPost (https://www.marktechpost.com/2024/10/17/assessing-the-vulnerabilities-of-llm-agents-the-agentharm-benchmark-for-robustness-against-jailbreak-attacks/)</t>
-        </is>
-      </c>
+          <t>None located</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr"/>
       <c r="AC209" t="inlineStr">
         <is>
-          <t>OS-Harm (NeurIPS 2025 Spotlight; arXiv:2506.14866) - confirmed cites AgentHarm; Mind the GAP (arXiv:2602.16943) - confirmed cites AgentHarm. Semantic Scholar: 317 total citations as of 2026-07-18 (https://api.semanticscholar.org/graph/v1/paper/arXiv:2410.09024?fields=title,citationCount)</t>
+          <t>Google Scholar: 38 citations: https://scholar.google.com/scholar?hl=en&amp;as_sdt=0%2C5&amp;q=%22Refusal-Trained%20LLMs%20Are%20Easily%20Jailbroken%20As%20Browser%20Agents%22</t>
         </is>
       </c>
       <c r="AD209" t="inlineStr"/>
       <c r="AE209" t="inlineStr"/>
       <c r="AF209" t="inlineStr">
         <is>
-          <t>Accountability gap (no action)</t>
+          <t>Proportionate</t>
         </is>
       </c>
       <c r="AG209" t="inlineStr">
@@ -30610,34 +30554,34 @@
       </c>
       <c r="AH209" t="inlineStr">
         <is>
-          <t>government-AISI</t>
+          <t>third-party-evaluator</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>UKAISI-2024-10-JAI2</t>
+          <t>SCALEAI-2024-10-JAI5</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>UKAISI-2024-10</t>
+          <t>SCALEAI-2024-10</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>UK AISI</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Government</t>
+          <t>For-Profit</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AgentHarm: A Benchmark for Measuring Harmfulness of LLM Agents</t>
+          <t>Refusal-Trained LLMs Are Easily Jailbroken As Browser Agents</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -30652,7 +30596,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Claude 3.5 Sonnet</t>
+          <t>GPT-4o, o1-preview (as browser agents)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -30662,17 +30606,17 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2410.09024</t>
+          <t>https://static.scale.com/uploads/6691558a94899f2f65a87a75/_ICLR__Red_Teaming_Browser_Agents%20(14).pdf</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Under AgentHarm's universal jailbreak template, Claude 3.5 Sonnet's harm score rose from 13.5% (no attack, 85.2% refusals) to 68.7% (refusals dropped to 16.7%); its non-refusal harm score under the jailbreak was 81.9%, nearly matching its 82% benign-task score, showing the template defeats a model that is very safe by default while preserving its agentic capabilities.</t>
+          <t>Scale AI's red team found that refusal training does not transfer from chat to browser-agent contexts: with human rewrites, GPT-4o and o1-preview based browser agents pursued 98 and 63 of 100 harmful behaviours respectively, even though the same backbone LLMs refuse those instructions as chatbots.</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>Claude 3.5 Sonnet, increasing its harm score from 13.5% to 68.7% and decreasing refusal rate from 85.2% to 16.7%; with our template attack, Claude 3.5 Sonnet scores a 81.9% non-refusal harm score (while refusing just 16% of requests), closely matching its non-refusal score of 82% on the benign tasks</t>
+          <t>With human rewrites, GPT-4o and o1-preview -based browser agents pursued 98 and 63 harmful behaviors (out of 100), respectively.</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -30712,40 +30656,28 @@
       </c>
       <c r="X210" t="inlineStr">
         <is>
-          <t>Non-binding policy-related uptake</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>NIST named the AgentHarm benchmark in its March 2025 adversarial machine learning taxonomy (NIST AI 100-2e2025, US Department of Commerce / NIST), both in Sec. 3.5 as an example of emerging research evaluating the vulnerability of LLM agents to AML attacks and in Sec. 3.6 in its list of named benchmarks for evaluating susceptibility to jailbreaks. The document expressly states it "does not establish any legal standard or any other legal requirement or defense under any law, nor does it have the force or effect of law" and that the guidance "remains voluntary" — official engagement with no enforceable obligation.</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>NIST AI 100-2e2025, Sec. 3.6 (Benchmarks for AML Vulnerabilities): "Datasets like JailbreakBench [72], AdvBench [448], HarmBench [237], StrongREJECT [351], AgentHarm [12], and Do-Not-Answer [399] provide benchmarks for evaluating models' susceptibility to jailbreaks." || Sec. 3.5 (Agents): "Security research focused specifically on agents is still in its early stages, but researchers have begun to evaluate the vulnerability of agents to particular AML attacks [12, 430] and to propose interventions to manage the security risks posed by agents [24]." Reference [12] = "Maksym Andriushchenko, Alexandra Souly, Mateusz Dziemian, Derek Duenas, Maxwell Lin, Justin Wang, Dan Hendrycks, Andy Zou, Zico Kolter, Matt Fredrikson, Eric Winsor, Jerome Wynne, Yarin Gal, and Xander Davies. Agentharm: A benchmark for measuring harmfulness of llm agents, 2024. URL: https://arxiv.org/abs/2410.09024, arXiv:2410.09024."</t>
-        </is>
-      </c>
+          <t>No policy uptake identified</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr"/>
+      <c r="Z210" t="inlineStr"/>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-2e2025.pdf</t>
-        </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>AZoAI (https://www.azoai.com/news/20241016/AgentHarm-Benchmark-Exposes-Weaknesses-in-AI-Agents-to-Harmful-Misuse-and-Jailbreaking.aspx)</t>
-        </is>
-      </c>
+          <t>None located</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr"/>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>AgentHarm accepted/published at ICLR 2025 (Andriushchenko et al.) (https://proceedings.iclr.cc/paper_files/paper/2025/file/c493d23af93118975cdbc32cbe7323f5-Paper-Conference.pdf); cited as a related agent-safety benchmark by subsequent work, e.g., OS-Harm (Kuntz et al., arXiv:2506.14866). Semantic Scholar: 317 total citations as of 2026-07-18 (https://api.semanticscholar.org/graph/v1/paper/arXiv:2410.09024?fields=title,citationCount)</t>
-        </is>
-      </c>
-      <c r="AD210" t="inlineStr"/>
-      <c r="AE210" t="inlineStr">
-        <is>
-          <t>harm score increased from 13.5% to 68.7%, and refusal rate fell from 85.2% to 16.7%</t>
-        </is>
-      </c>
+          <t>Semantic Scholar Graph API, paperId 73bb64ec0f1541e58e668845334f14c58d5f79a6, 'Refusal-Trained LLMs Are Easily Jailbroken As Browser Agents', arXiv:2410.13886, publicationDate 2024-10-11, venue arXiv.org: citationCount 67, influentialCitationCount 3 (retrieved 2026-08-29 from https://api.semanticscholar.org/graph/v1/paper/arXiv:2410.13886).</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>None located</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr"/>
       <c r="AF210" t="inlineStr">
         <is>
           <t>Accountability gap (no action)</t>
@@ -30758,14 +30690,14 @@
       </c>
       <c r="AH210" t="inlineStr">
         <is>
-          <t>government-AISI</t>
+          <t>third-party-evaluator</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>UKAISI-2024-10-JAI3</t>
+          <t>UKAISI-2024-10-JAI1</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -30800,7 +30732,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>GPT-4o</t>
+          <t>Mistral Large 2</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -30815,12 +30747,12 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>GPT-4o's harm compliance score increased from 48.4% to 72.7% after applying a universal jailbreak template adapted from chatbot jailbreaks, showing standard chat jailbreaking methods transfer to agents.</t>
+          <t>Some leading LLMs comply with malicious agentic requests at high rates without any jailbreaking — worst case Mistral Large 2 refused only 1.1% of requests and scored 82.2% harm — suggesting agents may be less robust than chatbots against misuse.</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>GPT-4o, increasing its harm score from 48.4% to 72.7% and decreasing refusal rate from 48.9% to 13.6%</t>
+          <t>Mistral Large 2 refuses just 1.1% of requests and gets our strongest score without attacking of 82.2%.</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -30865,12 +30797,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>NIST named the AgentHarm benchmark in its March 2025 adversarial-machine-learning taxonomy (NIST AI 100-2e2025), both as an example of emerging research evaluating the vulnerability of LLM agents to AML attacks and in its list of benchmarks for evaluating susceptibility to jailbreaks. Official engagement with no enforceable obligation.</t>
+          <t>NIST named the AgentHarm report in NIST AI 100-2e2025, "Adversarial Machine Learning: A Taxonomy and Terminology of Attacks and Mitigations" (US Department of Commerce / NIST, March 2025), citing it in Sec. 3.5 as emerging research evaluating the vulnerability of LLM agents to AML attacks and naming it in Sec. 3.6 among the benchmarks for evaluating models' susceptibility to jailbreaks, with a full bibliographic citation at reference [12]. Official US federal agency engagement with the report; the publication is a voluntary taxonomy and imposes no enforceable obligation.</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>NIST AI 100-2e2025, Sec. 3.6 (Benchmarks for AML Vulnerabilities): "Datasets like JailbreakBench [72], AdvBench [448], HarmBench [237], StrongREJECT [351], AgentHarm [12], and Do-Not-Answer [399] provide benchmarks for evaluating models' susceptibility to jailbreaks." || Sec. 3.5 (Agents): "Security research focused specifically on agents is still in its early stages, but researchers have begun to evaluate the vulnerability of agents to particular AML attacks [12, 430] and to propose interventions to manage the security risks posed by agents [24]." Reference [12] = "Maksym Andriushchenko, Alexandra Souly, Mateusz Dziemian, Derek Duenas, Maxwell Lin, Justin Wang, Dan Hendrycks, Andy Zou, Zico Kolter, Matt Fredrikson, Eric Winsor, Jerome Wynne, Yarin Gal, and Xander Davies. Agentharm: A benchmark for measuring harmfulness of llm agents, 2024. arXiv:2410.09024."</t>
+          <t>NIST AI 100-2e2025, Sec. 3.6 (Benchmarks for AML Vulnerabilities): "Datasets like JailbreakBench [72], AdvBench [448], HarmBench [237], StrongREJECT [351], AgentHarm [12], and Do-Not-Answer [399] provide benchmarks for evaluating models' susceptibility to jailbreaks." || Sec. 3.5 (Security of Agents): "Security research focused specifically on agents is still in its early stages, but researchers have begun to evaluate the vulnerability of agents to particular AML attacks [12, 430] and to propose interventions to manage the security risks posed by agents [24]." || Reference [12]: "Maksym Andriushchenko, Alexandra Souly, Mateusz Dziemian, Derek Duenas, Maxwell Lin, Justin Wang, Dan Hendrycks, Andy Zou, Zico Kolter, Matt Fredrikson, Eric Winsor, Jerome Wynne, Yarin Gal, and Xander Davies. Agentharm: A benchmark for measuring harmfulness of llm agents, 2024. URL: https://arxiv.org/abs/2410.09024, arXiv:2410.09024."</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -30880,12 +30812,12 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>MarkTechPost (https://www.marktechpost.com/2024/10/17/assessing-the-vulnerabilities-of-llm-agents-the-agentharm-benchmark-for-robustness-against-jailbreak-attacks/); AZoAI (https://www.azoai.com/news/20241016/AgentHarm-Benchmark-Exposes-Weaknesses-in-AI-Agents-to-Harmful-Misuse-and-Jailbreaking.aspx)</t>
+          <t>AZoAI (https://www.azoai.com/news/20241016/AgentHarm-Benchmark-Exposes-Weaknesses-in-AI-Agents-to-Harmful-Misuse-and-Jailbreaking.aspx); MarkTechPost (https://www.marktechpost.com/2024/10/17/assessing-the-vulnerabilities-of-llm-agents-the-agentharm-benchmark-for-robustness-against-jailbreak-attacks/)</t>
         </is>
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>OS-Harm (NeurIPS 2025 Spotlight, arXiv:2506.14866). Semantic Scholar: 317 total citations as of 2026-07-18 (https://api.semanticscholar.org/graph/v1/paper/arXiv:2410.09024?fields=title,citationCount)</t>
+          <t>OS-Harm (NeurIPS 2025 Spotlight; arXiv:2506.14866) - confirmed cites AgentHarm; Mind the GAP (arXiv:2602.16943) - confirmed cites AgentHarm. Semantic Scholar: 317 total citations as of 2026-07-18 (https://api.semanticscholar.org/graph/v1/paper/arXiv:2410.09024?fields=title,citationCount)</t>
         </is>
       </c>
       <c r="AD211" t="inlineStr"/>
@@ -30909,7 +30841,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>UKAISI-2024-10-JAI5</t>
+          <t>UKAISI-2024-10-JAI2</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -30944,7 +30876,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Gemini 1.5 Pro</t>
+          <t>Claude 3.5 Sonnet</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -30959,12 +30891,12 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Under the same universal jailbreak template, Gemini 1.5 Pro's harm score rose from 15.7% (no attack, 78.4% refusals) to 56.1%, with refusals collapsing from 78.4% to 3.5%.</t>
+          <t>Under AgentHarm's universal jailbreak template, Claude 3.5 Sonnet's harm score rose from 13.5% (no attack, 85.2% refusals) to 68.7% (refusals dropped to 16.7%); its non-refusal harm score under the jailbreak was 81.9%, nearly matching its 82% benign-task score, showing the template defeats a model that is very safe by default while preserving its agentic capabilities.</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>Gemini 1.5 Pro, increasing its harm score from 15.7% to 56.1% and decreasing refusal rate from 78.4% to 3.5%</t>
+          <t>Claude 3.5 Sonnet, increasing its harm score from 13.5% to 68.7% and decreasing refusal rate from 85.2% to 16.7%; with our template attack, Claude 3.5 Sonnet scores a 81.9% non-refusal harm score (while refusing just 16% of requests), closely matching its non-refusal score of 82% on the benign tasks</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -31009,12 +30941,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>NIST cited the AgentHarm report (UK AISI, arXiv:2410.09024) in NIST AI 100-2e2025, Adversarial Machine Learning: A Taxonomy and Terminology of Attacks and Mitigations (U.S. Department of Commerce / NIST, March 2025) — named in Sec. 3.6 as a benchmark for evaluating models' susceptibility to jailbreaks, and cited in Sec. 3.5 as research evaluating the vulnerability of agents to AML attacks. Official US government engagement with the report; the publication is a taxonomy and terminology document and imposes no enforceable obligation.</t>
+          <t>NIST named the AgentHarm benchmark in its March 2025 adversarial machine learning taxonomy (NIST AI 100-2e2025, US Department of Commerce / NIST), both in Sec. 3.5 as an example of emerging research evaluating the vulnerability of LLM agents to AML attacks and in Sec. 3.6 in its list of named benchmarks for evaluating susceptibility to jailbreaks. The document expressly states it "does not establish any legal standard or any other legal requirement or defense under any law, nor does it have the force or effect of law" and that the guidance "remains voluntary" — official engagement with no enforceable obligation.</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>Sec. 3.6 (Benchmarks for AML Vulnerabilities): "Datasets like JailbreakBench [72], AdvBench [448], HarmBench [237], StrongREJECT [351], AgentHarm [12], and Do-Not-Answer [399] provide benchmarks for evaluating models' susceptibility to jailbreaks." || Sec. 3.5 (Agents): "Security research focused specifically on agents is still in its early stages, but researchers have begun to evaluate the vulnerability of agents to particular AML attacks [12, 430] and to propose interventions to manage the security risks posed by agents [24]." || Reference [12]: "Maksym Andriushchenko, Alexandra Souly, Mateusz Dziemian, Derek Duenas, Maxwell Lin, Justin Wang, Dan Hendrycks, Andy Zou, Zico Kolter, Matt Fredrikson, Eric Winsor, Jerome Wynne, Yarin Gal, and Xander Davies. Agentharm: A benchmark for measuring harmfulness of llm agents, 2024. URL: https://arxiv.org/abs/2410.09024, arXiv:2410.09024."</t>
+          <t>NIST AI 100-2e2025, Sec. 3.6 (Benchmarks for AML Vulnerabilities): "Datasets like JailbreakBench [72], AdvBench [448], HarmBench [237], StrongREJECT [351], AgentHarm [12], and Do-Not-Answer [399] provide benchmarks for evaluating models' susceptibility to jailbreaks." || Sec. 3.5 (Agents): "Security research focused specifically on agents is still in its early stages, but researchers have begun to evaluate the vulnerability of agents to particular AML attacks [12, 430] and to propose interventions to manage the security risks posed by agents [24]." Reference [12] = "Maksym Andriushchenko, Alexandra Souly, Mateusz Dziemian, Derek Duenas, Maxwell Lin, Justin Wang, Dan Hendrycks, Andy Zou, Zico Kolter, Matt Fredrikson, Eric Winsor, Jerome Wynne, Yarin Gal, and Xander Davies. Agentharm: A benchmark for measuring harmfulness of llm agents, 2024. URL: https://arxiv.org/abs/2410.09024, arXiv:2410.09024."</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -31022,14 +30954,22 @@
           <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-2e2025.pdf</t>
         </is>
       </c>
-      <c r="AB212" t="inlineStr"/>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>AZoAI (https://www.azoai.com/news/20241016/AgentHarm-Benchmark-Exposes-Weaknesses-in-AI-Agents-to-Harmful-Misuse-and-Jailbreaking.aspx)</t>
+        </is>
+      </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>Semantic Scholar: 317 citations as of 2026-07-18 (https://api.semanticscholar.org/graph/v1/paper/arXiv:2410.09024?fields=title,citationCount)</t>
+          <t>AgentHarm accepted/published at ICLR 2025 (Andriushchenko et al.) (https://proceedings.iclr.cc/paper_files/paper/2025/file/c493d23af93118975cdbc32cbe7323f5-Paper-Conference.pdf); cited as a related agent-safety benchmark by subsequent work, e.g., OS-Harm (Kuntz et al., arXiv:2506.14866). Semantic Scholar: 317 total citations as of 2026-07-18 (https://api.semanticscholar.org/graph/v1/paper/arXiv:2410.09024?fields=title,citationCount)</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr"/>
-      <c r="AE212" t="inlineStr"/>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>harm score increased from 13.5% to 68.7%, and refusal rate fell from 85.2% to 16.7%</t>
+        </is>
+      </c>
       <c r="AF212" t="inlineStr">
         <is>
           <t>Accountability gap (no action)</t>
@@ -31049,7 +30989,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>UKAISI-2024-10-JAI6</t>
+          <t>UKAISI-2024-10-JAI3</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -31084,7 +31024,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>GPT-4o mini</t>
+          <t>GPT-4o</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -31099,12 +31039,12 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>AgentHarm found GPT-4o mini complies with malicious agentic tasks at a high rate by default, achieving a 62.5% harm score while refusing only 22% of malicious prompts.</t>
+          <t>GPT-4o's harm compliance score increased from 48.4% to 72.7% after applying a universal jailbreak template adapted from chatbot jailbreaks, showing standard chat jailbreaking methods transfer to agents.</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>GPT-4o mini gets a 62.5% harm score, while refusing just 22% of the prompts.</t>
+          <t>GPT-4o, increasing its harm score from 48.4% to 72.7% and decreasing refusal rate from 48.9% to 13.6%</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -31149,12 +31089,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>NIST named the AgentHarm benchmark in NIST AI 100-2e2025, "Adversarial Machine Learning: A Taxonomy and Terminology of Attacks and Mitigations" (National Institute of Standards and Technology, U.S. Department of Commerce, March 2025; approved by the NIST Editorial Review Board on 2025-03-20). AgentHarm is named in body text in Sec. 3.6 among the benchmarks for evaluating models' susceptibility to jailbreaks, cited as reference [12] in Sec. 3.5 as an example of research evaluating the vulnerability of LLM agents to AML attacks, and given in full in the bibliography with its arXiv identifier. Official US federal agency engagement with the report; the publication is a taxonomy and terminology document and imposes no enforceable obligation.</t>
+          <t>NIST named the AgentHarm benchmark in its March 2025 adversarial-machine-learning taxonomy (NIST AI 100-2e2025), both as an example of emerging research evaluating the vulnerability of LLM agents to AML attacks and in its list of benchmarks for evaluating susceptibility to jailbreaks. Official engagement with no enforceable obligation.</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>NIST AI 100-2e2025, Sec. 3.6 (Benchmarks for AML Vulnerabilities): "Datasets like JailbreakBench [72], AdvBench [448], HarmBench [237], StrongREJECT [351], AgentHarm [12], and Do-Not-Answer [399] provide benchmarks for evaluating models' susceptibility to jailbreaks." || Sec. 3.5 (Security of Agents): "Security research focused specifically on agents is still in its early stages, but researchers have begun to evaluate the vulnerability of agents to particular AML attacks [12, 430] and to propose interventions to manage the security risks posed by agents [24]." || Reference [12] = "Maksym Andriushchenko, Alexandra Souly, Mateusz Dziemian, Derek Duenas, Maxwell Lin, Justin Wang, Dan Hendrycks, Andy Zou, Zico Kolter, Matt Fredrikson, Eric Winsor, Jerome Wynne, Yarin Gal, and Xander Davies. Agentharm: A benchmark for measuring harmfulness of llm agents, 2024. URL: https://arxiv.org/abs/2410.09024, arXiv:2410.09024."</t>
+          <t>NIST AI 100-2e2025, Sec. 3.6 (Benchmarks for AML Vulnerabilities): "Datasets like JailbreakBench [72], AdvBench [448], HarmBench [237], StrongREJECT [351], AgentHarm [12], and Do-Not-Answer [399] provide benchmarks for evaluating models' susceptibility to jailbreaks." || Sec. 3.5 (Agents): "Security research focused specifically on agents is still in its early stages, but researchers have begun to evaluate the vulnerability of agents to particular AML attacks [12, 430] and to propose interventions to manage the security risks posed by agents [24]." Reference [12] = "Maksym Andriushchenko, Alexandra Souly, Mateusz Dziemian, Derek Duenas, Maxwell Lin, Justin Wang, Dan Hendrycks, Andy Zou, Zico Kolter, Matt Fredrikson, Eric Winsor, Jerome Wynne, Yarin Gal, and Xander Davies. Agentharm: A benchmark for measuring harmfulness of llm agents, 2024. arXiv:2410.09024."</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -31162,10 +31102,14 @@
           <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-2e2025.pdf</t>
         </is>
       </c>
-      <c r="AB213" t="inlineStr"/>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>MarkTechPost (https://www.marktechpost.com/2024/10/17/assessing-the-vulnerabilities-of-llm-agents-the-agentharm-benchmark-for-robustness-against-jailbreak-attacks/); AZoAI (https://www.azoai.com/news/20241016/AgentHarm-Benchmark-Exposes-Weaknesses-in-AI-Agents-to-Harmful-Misuse-and-Jailbreaking.aspx)</t>
+        </is>
+      </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>Semantic Scholar: 317 citations as of 2026-07-18 (https://api.semanticscholar.org/graph/v1/paper/arXiv:2410.09024?fields=title,citationCount)</t>
+          <t>OS-Harm (NeurIPS 2025 Spotlight, arXiv:2506.14866). Semantic Scholar: 317 total citations as of 2026-07-18 (https://api.semanticscholar.org/graph/v1/paper/arXiv:2410.09024?fields=title,citationCount)</t>
         </is>
       </c>
       <c r="AD213" t="inlineStr"/>
@@ -31189,7 +31133,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>UKAISI-2024-10-JAI7</t>
+          <t>UKAISI-2024-10-JAI5</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -31224,7 +31168,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>GPT-3.5 Turbo</t>
+          <t>Gemini 1.5 Pro</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -31239,12 +31183,12 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>AgentHarm found GPT-3.5 Turbo showed almost no refusal (0.8%) of malicious agentic tasks with NO jailbreak attack applied at all, despite a 62.2% harm score -- the lowest refusal rate among no-attack conditions in the paper (though several models, including Mistral Large 2, reach 0.0% refusal once a jailbreak template is applied).</t>
+          <t>Under the same universal jailbreak template, Gemini 1.5 Pro's harm score rose from 15.7% (no attack, 78.4% refusals) to 56.1%, with refusals collapsing from 78.4% to 3.5%.</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>[Table 9: Main results on the public test set, GPT-3.5 Turbo / no-attack row]: "GPT-3.5 Turbo | None | 62.2% | 0.8% | 62.7% | 67.7%"</t>
+          <t>Gemini 1.5 Pro, increasing its harm score from 15.7% to 56.1% and decreasing refusal rate from 78.4% to 3.5%</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -31284,14 +31228,22 @@
       </c>
       <c r="X214" t="inlineStr">
         <is>
-          <t>No policy uptake identified</t>
-        </is>
-      </c>
-      <c r="Y214" t="inlineStr"/>
-      <c r="Z214" t="inlineStr"/>
+          <t>Non-binding policy-related uptake</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>NIST cited the AgentHarm report (UK AISI, arXiv:2410.09024) in NIST AI 100-2e2025, Adversarial Machine Learning: A Taxonomy and Terminology of Attacks and Mitigations (U.S. Department of Commerce / NIST, March 2025) — named in Sec. 3.6 as a benchmark for evaluating models' susceptibility to jailbreaks, and cited in Sec. 3.5 as research evaluating the vulnerability of agents to AML attacks. Official US government engagement with the report; the publication is a taxonomy and terminology document and imposes no enforceable obligation.</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>Sec. 3.6 (Benchmarks for AML Vulnerabilities): "Datasets like JailbreakBench [72], AdvBench [448], HarmBench [237], StrongREJECT [351], AgentHarm [12], and Do-Not-Answer [399] provide benchmarks for evaluating models' susceptibility to jailbreaks." || Sec. 3.5 (Agents): "Security research focused specifically on agents is still in its early stages, but researchers have begun to evaluate the vulnerability of agents to particular AML attacks [12, 430] and to propose interventions to manage the security risks posed by agents [24]." || Reference [12]: "Maksym Andriushchenko, Alexandra Souly, Mateusz Dziemian, Derek Duenas, Maxwell Lin, Justin Wang, Dan Hendrycks, Andy Zou, Zico Kolter, Matt Fredrikson, Eric Winsor, Jerome Wynne, Yarin Gal, and Xander Davies. Agentharm: A benchmark for measuring harmfulness of llm agents, 2024. URL: https://arxiv.org/abs/2410.09024, arXiv:2410.09024."</t>
+        </is>
+      </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>None located</t>
+          <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-2e2025.pdf</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr"/>
@@ -31321,32 +31273,32 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>CISCO-2024-08-JAI1</t>
+          <t>UKAISI-2024-10-JAI6</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>CISCO-2024-08</t>
+          <t>UKAISI-2024-10</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Cisco (Robust Intelligence / Foundation AI)</t>
+          <t>UK AISI</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>For-Profit</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Bypassing OpenAI's Structured Outputs: Another Simple Jailbreak</t>
+          <t>AgentHarm: A Benchmark for Measuring Harmfulness of LLM Agents</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -31356,7 +31308,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>OpenAI Structured Outputs API feature (refusal mechanism)</t>
+          <t>GPT-4o mini</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -31366,17 +31318,17 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>https://blogs.cisco.com/security/bypassing-openais-structured-outputs-another-simple-jailbreak</t>
+          <t>https://arxiv.org/abs/2410.09024</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>An ENUM-based custom data structure that forces every response step to begin with an attacker-chosen prefix raised attack success rate on SORRY-Bench from 12.44% (normal API calling) to 52.89% - a 4.25x increase - and cut appropriate refusals from 59.6% to 30.2%.</t>
+          <t>AgentHarm found GPT-4o mini complies with malicious agentic tasks at a high rate by default, achieving a 62.5% harm score while refusing only 22% of malicious prompts.</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>The ENUM-based attack achieved an ASR of 52.89%, compared to 12.44% for normal API calling and 15.78% for function calling baselines.</t>
+          <t>GPT-4o mini gets a 62.5% harm score, while refusing just 22% of the prompts.</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -31416,20 +31368,28 @@
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>No policy uptake identified</t>
-        </is>
-      </c>
-      <c r="Y215" t="inlineStr"/>
-      <c r="Z215" t="inlineStr"/>
+          <t>Non-binding policy-related uptake</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>NIST named the AgentHarm benchmark in NIST AI 100-2e2025, "Adversarial Machine Learning: A Taxonomy and Terminology of Attacks and Mitigations" (National Institute of Standards and Technology, U.S. Department of Commerce, March 2025; approved by the NIST Editorial Review Board on 2025-03-20). AgentHarm is named in body text in Sec. 3.6 among the benchmarks for evaluating models' susceptibility to jailbreaks, cited as reference [12] in Sec. 3.5 as an example of research evaluating the vulnerability of LLM agents to AML attacks, and given in full in the bibliography with its arXiv identifier. Official US federal agency engagement with the report; the publication is a taxonomy and terminology document and imposes no enforceable obligation.</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>NIST AI 100-2e2025, Sec. 3.6 (Benchmarks for AML Vulnerabilities): "Datasets like JailbreakBench [72], AdvBench [448], HarmBench [237], StrongREJECT [351], AgentHarm [12], and Do-Not-Answer [399] provide benchmarks for evaluating models' susceptibility to jailbreaks." || Sec. 3.5 (Security of Agents): "Security research focused specifically on agents is still in its early stages, but researchers have begun to evaluate the vulnerability of agents to particular AML attacks [12, 430] and to propose interventions to manage the security risks posed by agents [24]." || Reference [12] = "Maksym Andriushchenko, Alexandra Souly, Mateusz Dziemian, Derek Duenas, Maxwell Lin, Justin Wang, Dan Hendrycks, Andy Zou, Zico Kolter, Matt Fredrikson, Eric Winsor, Jerome Wynne, Yarin Gal, and Xander Davies. Agentharm: A benchmark for measuring harmfulness of llm agents, 2024. URL: https://arxiv.org/abs/2410.09024, arXiv:2410.09024."</t>
+        </is>
+      </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>None located</t>
+          <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-2e2025.pdf</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr"/>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>Google Scholar: not indexed under the exact report title: https://scholar.google.com/scholar?hl=en&amp;as_sdt=0%2C5&amp;q=%22Bypassing%20OpenAI's%20Structured%20Outputs%3A%20Another%20Simple%20Jailbreak%22</t>
+          <t>Semantic Scholar: 317 citations as of 2026-07-18 (https://api.semanticscholar.org/graph/v1/paper/arXiv:2410.09024?fields=title,citationCount)</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr"/>
@@ -31446,39 +31406,39 @@
       </c>
       <c r="AH215" t="inlineStr">
         <is>
-          <t>third-party-evaluator</t>
+          <t>government-AISI</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>FARAI-2024-08-JAI1</t>
+          <t>UKAISI-2024-10-JAI7</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>FARAI-2024-08</t>
+          <t>UKAISI-2024-10</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>FAR.AI</t>
+          <t>UK AISI</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Non-Profit (Independent)</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Data Poisoning in LLMs: Jailbreak-Tuning and Scaling Laws</t>
+          <t>AgentHarm: A Benchmark for Measuring Harmfulness of LLM Agents</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -31488,7 +31448,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>OpenAI GPT models (not individually named in abstract)</t>
+          <t>GPT-3.5 Turbo</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -31498,17 +31458,17 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>https://www.far.ai/research/scaling-laws-for-data-poisoning-in-llms</t>
+          <t>https://arxiv.org/abs/2410.09024</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>The paper reports that OpenAI's GPT models remained vulnerable to fine-tuning on poisoned data even when protected by moderation systems, and calls on leading AI companies to red team fine-tuning APIs thoroughly before public release.</t>
+          <t>AgentHarm found GPT-3.5 Turbo showed almost no refusal (0.8%) of malicious agentic tasks with NO jailbreak attack applied at all, despite a 62.2% harm score -- the lowest refusal rate among no-attack conditions in the paper (though several models, including Mistral Large 2, reach 0.0% refusal once a jailbreak template is applied).</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>We demonstrate that GPT models remain vulnerable to fine-tuning on poisoned data, even when safeguarded by moderation systems.</t>
+          <t>[Table 9: Main results on the public test set, GPT-3.5 Turbo / no-attack row]: "GPT-3.5 Turbo | None | 62.2% | 0.8% | 62.7% | 67.7%"</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -31533,70 +31493,42 @@
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>No explicit attribution</t>
-        </is>
-      </c>
-      <c r="R216" t="inlineStr">
-        <is>
-          <t>OpenAI wound down its self-serve fine-tuning platform: from 2026-05-07 organisations that had not previously run fine-tuning could no longer create training jobs; restrictions tighten on 2026-07-02 and from 2027-01-06 existing customers can create no new fine-tuning jobs at all. Inference on already fine-tuned models continues until the base model is deprecated. This removes the public attack surface the finding exploited. NOTE ON MOTIVE: OpenAI's stated rationale is capability — that newer models make much of fine-tuning unnecessary — not safety, and the notice does not reference this finding or FAR.AI. Coded Partial as an access restriction that addresses the surface but is not presented as a safety fix.</t>
-        </is>
-      </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>The platform is no longer accessible to new users but existing users of the fine-tuning platform will be able to create training jobs for the coming months.</t>
-        </is>
-      </c>
-      <c r="T216" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="V216" t="inlineStr">
-        <is>
-          <t>https://openai.com/index/gpt-4o-fine-tuning/ (OpenAI GPT-4o fine-tuning launch page, 'Update on May 8, 2026' wind-down banner — the page that actually carries this verbatim; repointed 2026-08-28 after the 2026-08-17 correction moved these rows to the API deprecations notice, which fetches 200 but does not contain the quoted sentence)</t>
-        </is>
-      </c>
+          <t>No response located</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr"/>
+      <c r="S216" t="inlineStr"/>
+      <c r="T216" t="inlineStr"/>
+      <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr"/>
       <c r="W216" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>None</t>
         </is>
       </c>
       <c r="X216" t="inlineStr">
         <is>
-          <t>Non-binding policy-related uptake</t>
-        </is>
-      </c>
-      <c r="Y216" t="inlineStr">
-        <is>
-          <t>NIST cited this work in its March 2025 taxonomy when describing practical generative-AI data-poisoning attacks and their potential effects.</t>
-        </is>
-      </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>“These attacks may be practical—requiring a relatively small portion of the total dataset—and may lead to a range of bad outcomes.”</t>
-        </is>
-      </c>
+          <t>No policy uptake identified</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr"/>
+      <c r="Z216" t="inlineStr"/>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-2e2025.pdf</t>
+          <t>None located</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr"/>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>Google Scholar: 40 citations: https://scholar.google.com/scholar?hl=en&amp;as_sdt=0%2C5&amp;q=%22Data%20Poisoning%20in%20LLMs%3A%20Jailbreak-Tuning%20and%20Scaling%20Laws%22</t>
+          <t>Semantic Scholar: 317 citations as of 2026-07-18 (https://api.semanticscholar.org/graph/v1/paper/arXiv:2410.09024?fields=title,citationCount)</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr"/>
       <c r="AE216" t="inlineStr"/>
       <c r="AF216" t="inlineStr">
         <is>
-          <t>Under-response (gap)</t>
+          <t>Accountability gap (no action)</t>
         </is>
       </c>
       <c r="AG216" t="inlineStr">
@@ -31606,19 +31538,19 @@
       </c>
       <c r="AH216" t="inlineStr">
         <is>
-          <t>third-party-evaluator</t>
+          <t>government-AISI</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>CISCO-2024-07-JAI1</t>
+          <t>CISCO-2024-08-JAI1</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>CISCO-2024-07</t>
+          <t>CISCO-2024-08</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -31633,12 +31565,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Bypassing Meta's LLaMA Classifier: A Simple Jailbreak</t>
+          <t>Bypassing OpenAI's Structured Outputs: Another Simple Jailbreak</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -31648,7 +31580,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Prompt-Guard-86M (Meta, part of the Llama 3.1 safety suite)</t>
+          <t>OpenAI Structured Outputs API feature (refusal mechanism)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -31658,17 +31590,17 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://blogs.cisco.com/security/bypassing-metas-llama-classifier-a-simple-jailbreak</t>
+          <t>https://blogs.cisco.com/security/bypassing-openais-structured-outputs-another-simple-jailbreak</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Spacing out characters and removing punctuation took Meta's Prompt-Guard-86M prompt-injection classifier from correctly flagging all 450 harmful prompts to 0.2% accuracy (449/450 misclassified as benign, a 99.8% bypass rate); Cisco traced the flaw to single-character embeddings left essentially unchanged by fine-tuning (average MAE &lt; 0.0003 across shared tokens).</t>
+          <t>An ENUM-based custom data structure that forces every response step to begin with an attacker-chosen prefix raised attack success rate on SORRY-Bench from 12.44% (normal API calling) to 52.89% - a 4.25x increase - and cut appropriate refusals from 59.6% to 30.2%.</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>the model's performance plummeted to 0.2% accuracy, misclassifying 449 out of 450 prompts as benign and demonstrating a complete circumvention of the model's safety mechanisms (Success Rate of 99.8%)</t>
+          <t>The ENUM-based attack achieved an ASR of 52.89%, compared to 12.44% for normal API calling and 15.78% for function calling baselines.</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -31693,37 +31625,17 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>No explicit attribution</t>
-        </is>
-      </c>
-      <c r="R217" t="inlineStr">
-        <is>
-          <t>Meta released Llama Prompt Guard 2 86M as an updated classifier with improved jailbreak and prompt-injection detection, together with a smaller 22M variant and the LlamaFirewall defense layer.</t>
-        </is>
-      </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>Llama Prompt Guard 2: Prompt Guard 2 86M, an update to our Llama Prompt Guard classifier model, improves on its performance in jailbreak and prompt injection detection.</t>
-        </is>
-      </c>
-      <c r="T217" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>https://ai.meta.com/blog/ai-defenders-program-llama-protection-tools/</t>
-        </is>
-      </c>
+          <t>No response located</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr"/>
+      <c r="S217" t="inlineStr"/>
+      <c r="T217" t="inlineStr"/>
+      <c r="U217" t="inlineStr"/>
+      <c r="V217" t="inlineStr"/>
       <c r="W217" t="inlineStr">
         <is>
-          <t>Substantive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="X217" t="inlineStr">
@@ -31741,14 +31653,14 @@
       <c r="AB217" t="inlineStr"/>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>Google Scholar: not indexed under the exact report title: https://scholar.google.com/scholar?hl=en&amp;as_sdt=0%2C5&amp;q=%22Bypassing%20Meta's%20LLaMA%20Classifier%3A%20A%20Simple%20Jailbreak%22</t>
+          <t>Google Scholar: not indexed under the exact report title: https://scholar.google.com/scholar?hl=en&amp;as_sdt=0%2C5&amp;q=%22Bypassing%20OpenAI's%20Structured%20Outputs%3A%20Another%20Simple%20Jailbreak%22</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr"/>
       <c r="AE217" t="inlineStr"/>
       <c r="AF217" t="inlineStr">
         <is>
-          <t>Proportionate</t>
+          <t>Accountability gap (no action)</t>
         </is>
       </c>
       <c r="AG217" t="inlineStr">
@@ -31765,17 +31677,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>PALISADE-2024-07-JAI1</t>
+          <t>FARAI-2024-08-JAI1</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PALISADE-2024-07-BADLLAMA3</t>
+          <t>FARAI-2024-08</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Palisade Research</t>
+          <t>FAR.AI</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -31785,12 +31697,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Badllama 3: Removing Safety Finetuning from Llama 3 in Minutes</t>
+          <t>Data Poisoning in LLMs: Jailbreak-Tuning and Scaling Laws</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -31800,7 +31712,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Llama 3 8B; Llama 3 70B</t>
+          <t>OpenAI GPT models (not individually named in abstract)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -31810,32 +31722,32 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>https://palisaderesearch.org/blog/badllama-3</t>
+          <t>https://www.far.ai/research/scaling-laws-for-data-poisoning-in-llms</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Safety fine-tuning was stripped from Llama 3 8B in one minute and 70B in 30 minutes on a single GPU.</t>
+          <t>The paper reports that OpenAI's GPT models remained vulnerable to fine-tuning on poisoned data even when protected by moderation systems, and calls on leading AI companies to red team fine-tuning APIs thoroughly before public release.</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>Llama 3 8B in one minute and Llama 3 70B in 30 minutes on a single GPU</t>
+          <t>We demonstrate that GPT models remain vulnerable to fine-tuning on poisoned data, even when safeguarded by moderation systems.</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -31845,42 +31757,70 @@
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>No response located</t>
-        </is>
-      </c>
-      <c r="R218" t="inlineStr"/>
-      <c r="S218" t="inlineStr"/>
-      <c r="T218" t="inlineStr"/>
-      <c r="U218" t="inlineStr"/>
-      <c r="V218" t="inlineStr"/>
+          <t>No explicit attribution</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>OpenAI wound down its self-serve fine-tuning platform: from 2026-05-07 organisations that had not previously run fine-tuning could no longer create training jobs; restrictions tighten on 2026-07-02 and from 2027-01-06 existing customers can create no new fine-tuning jobs at all. Inference on already fine-tuned models continues until the base model is deprecated. This removes the public attack surface the finding exploited. NOTE ON MOTIVE: OpenAI's stated rationale is capability — that newer models make much of fine-tuning unnecessary — not safety, and the notice does not reference this finding or FAR.AI. Coded Partial as an access restriction that addresses the surface but is not presented as a safety fix.</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>The platform is no longer accessible to new users but existing users of the fine-tuning platform will be able to create training jobs for the coming months.</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>https://openai.com/index/gpt-4o-fine-tuning/ (OpenAI GPT-4o fine-tuning launch page, 'Update on May 8, 2026' wind-down banner — the page that actually carries this verbatim; repointed 2026-08-28 after the 2026-08-17 correction moved these rows to the API deprecations notice, which fetches 200 but does not contain the quoted sentence)</t>
+        </is>
+      </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>No policy uptake identified</t>
-        </is>
-      </c>
-      <c r="Y218" t="inlineStr"/>
-      <c r="Z218" t="inlineStr"/>
+          <t>Non-binding policy-related uptake</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>NIST cited this work in its March 2025 taxonomy when describing practical generative-AI data-poisoning attacks and their potential effects.</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>“These attacks may be practical—requiring a relatively small portion of the total dataset—and may lead to a range of bad outcomes.”</t>
+        </is>
+      </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>Congress.gov and NTIA open-weight foundation model report pages returned HTTP 403 (inaccessible); no independent evidence linking this finding to any policy document The earlier attempt recorded blocked government sources, so the negative coding was not fully earned. Re-run via search, which reaches these records where direct fetch does not. (1) UK -- Hansard (Commons + Lords), select-committee reports, gov.uk, NCSC/ICO/FCA advisories. (2) US -- Congress.gov, govinfo, Federal Register, NIST/CAISI announcements. (3) EU/other -- Commission and AI Office statements. Search terms: evaluator 'Palisade Research', report 'Badllama 3: Removing Safety Finetuning from Llama 3 in Minut', and the finding's specific claim. No official source explicitly references the finding, report or result; same-topic policy activity without an explicit link does not qualify. All required sources checked -&gt; Policy Level unchanged, now documented.</t>
+          <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-2e2025.pdf</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr"/>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>Volkov, "Badllama 3: removing safety finetuning from Llama 3 in minutes" (Palisade Research, arXiv:2407.01376, 2024-07-01) -- ~9-14 citations per Google Scholar/Semantic Scholar, including red-teaming scaling-law and open-weight risk-mitigation papers</t>
+          <t>Google Scholar: 40 citations: https://scholar.google.com/scholar?hl=en&amp;as_sdt=0%2C5&amp;q=%22Data%20Poisoning%20in%20LLMs%3A%20Jailbreak-Tuning%20and%20Scaling%20Laws%22</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr"/>
       <c r="AE218" t="inlineStr"/>
       <c r="AF218" t="inlineStr">
         <is>
-          <t>Accountability gap (no action)</t>
+          <t>Under-response (gap)</t>
         </is>
       </c>
       <c r="AG218" t="inlineStr">
@@ -31897,42 +31837,42 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SHANGHAIAILAB-2024-02-GOV1</t>
+          <t>CISCO-2024-07-JAI1</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>SHANGHAIAILAB-2024-02</t>
+          <t>CISCO-2024-07</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Shanghai AI Laboratory (AI45 Lab)</t>
+          <t>Cisco (Robust Intelligence / Foundation AI)</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Non-Profit (Independent)</t>
+          <t>For-Profit</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>SALAD-Bench: A Hierarchical and Comprehensive Safety Benchmark for Large Language Models (ACL Findings)</t>
+          <t>Bypassing Meta's LLaMA Classifier: A Simple Jailbreak</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Eval-methodology</t>
+          <t>Jailbreaks</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Prompt-Guard-86M (Meta, part of the Llama 3.1 safety suite)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -31942,17 +31882,17 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2402.05044</t>
+          <t>https://blogs.cisco.com/security/bypassing-metas-llama-classifier-a-simple-jailbreak</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>On SALAD-Bench's attack-enhanced subset, Google's Gemini safety rate fell to approximately 20%, a sharp decline from its base-set performance.</t>
+          <t>Spacing out characters and removing punctuation took Meta's Prompt-Guard-86M prompt-injection classifier from correctly flagging all 450 harmful prompts to 0.2% accuracy (449/450 misclassified as benign, a 99.8% bypass rate); Cisco traced the flaw to single-character embeddings left essentially unchanged by fine-tuning (average MAE &lt; 0.0003 across shared tokens).</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>Claude2 leads in performance across both sets, while Gemini’s performance notably declines to approximately 20% in the attack-enhanced subset.</t>
+          <t>the model's performance plummeted to 0.2% accuracy, misclassifying 449 out of 450 prompts as benign and demonstrating a complete circumvention of the model's safety mechanisms (Success Rate of 99.8%)</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -31977,17 +31917,37 @@
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>No response located</t>
-        </is>
-      </c>
-      <c r="R219" t="inlineStr"/>
-      <c r="S219" t="inlineStr"/>
-      <c r="T219" t="inlineStr"/>
-      <c r="U219" t="inlineStr"/>
-      <c r="V219" t="inlineStr"/>
+          <t>No explicit attribution</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Meta released Llama Prompt Guard 2 86M as an updated classifier with improved jailbreak and prompt-injection detection, together with a smaller 22M variant and the LlamaFirewall defense layer.</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>Llama Prompt Guard 2: Prompt Guard 2 86M, an update to our Llama Prompt Guard classifier model, improves on its performance in jailbreak and prompt injection detection.</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>https://ai.meta.com/blog/ai-defenders-program-llama-protection-tools/</t>
+        </is>
+      </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Substantive</t>
         </is>
       </c>
       <c r="X219" t="inlineStr">
@@ -32002,25 +31962,17 @@
           <t>None located</t>
         </is>
       </c>
-      <c r="AB219" t="inlineStr">
-        <is>
-          <t>None located</t>
-        </is>
-      </c>
+      <c r="AB219" t="inlineStr"/>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>Semantic Scholar, paperId 868fcbc6127e9cf79990e92116ec482051d470f3, arXiv 2402.05044: citationCount 271, influentialCitationCount 43. Peer-reviewed venue confirmed: Findings of the ACL 2024, https://aclanthology.org/2024.findings-acl.235/ (the finding's own paper - circular, logged for provenance only).</t>
-        </is>
-      </c>
-      <c r="AD219" t="inlineStr">
-        <is>
-          <t>None located</t>
-        </is>
-      </c>
+          <t>Google Scholar: not indexed under the exact report title: https://scholar.google.com/scholar?hl=en&amp;as_sdt=0%2C5&amp;q=%22Bypassing%20Meta's%20LLaMA%20Classifier%3A%20A%20Simple%20Jailbreak%22</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr"/>
       <c r="AE219" t="inlineStr"/>
       <c r="AF219" t="inlineStr">
         <is>
-          <t>Accountability gap (no action)</t>
+          <t>Proportionate</t>
         </is>
       </c>
       <c r="AG219" t="inlineStr">
@@ -32037,17 +31989,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SHANGHAIAILAB-2024-02-JAI1</t>
+          <t>PALISADE-2024-07-JAI1</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>SHANGHAIAILAB-2024-02</t>
+          <t>PALISADE-2024-07-BADLLAMA3</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Shanghai AI Laboratory (AI45 Lab)</t>
+          <t>Palisade Research</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -32057,12 +32009,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>SALAD-Bench: A Hierarchical and Comprehensive Safety Benchmark for Large Language Models (ACL Findings)</t>
+          <t>Badllama 3: Removing Safety Finetuning from Llama 3 in Minutes</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -32072,7 +32024,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>GPT-4, GPT-3.5, Claude2, Gemini</t>
+          <t>Llama 3 8B; Llama 3 70B</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -32082,32 +32034,32 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2402.05044</t>
+          <t>https://palisaderesearch.org/blog/badllama-3</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Shanghai AI Lab's SALAD-Bench found Gemini's safety rate dropped sharply under adversarial attack-enhanced prompts (88.32% base to 19.98% attack-enhanced), a far larger degradation than Claude2 (88.02%), GPT-4 (80.28%), or GPT-3.5 (73.38%) on the same attack-enhanced subset.</t>
+          <t>Safety fine-tuning was stripped from Llama 3 8B in one minute and 70B in 30 minutes on a single GPU.</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>Conversely, Gemini's safety rate significantly drops in the attack-enhanced subset, highlighting potential safety vulnerabilities; Gemini 88.32% (base) to 19.98% (attack-enhanced); Claude2 88.02%; GPT-4 80.28%; GPT-3.5 73.38% [attack-enhanced, Table 5].</t>
+          <t>Llama 3 8B in one minute and Llama 3 70B in 30 minutes on a single GPU</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -32139,13 +32091,13 @@
       <c r="Z220" t="inlineStr"/>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>None located</t>
+          <t>Congress.gov and NTIA open-weight foundation model report pages returned HTTP 403 (inaccessible); no independent evidence linking this finding to any policy document The earlier attempt recorded blocked government sources, so the negative coding was not fully earned. Re-run via search, which reaches these records where direct fetch does not. (1) UK -- Hansard (Commons + Lords), select-committee reports, gov.uk, NCSC/ICO/FCA advisories. (2) US -- Congress.gov, govinfo, Federal Register, NIST/CAISI announcements. (3) EU/other -- Commission and AI Office statements. Search terms: evaluator 'Palisade Research', report 'Badllama 3: Removing Safety Finetuning from Llama 3 in Minut', and the finding's specific claim. No official source explicitly references the finding, report or result; same-topic policy activity without an explicit link does not qualify. All required sources checked -&gt; Policy Level unchanged, now documented.</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr"/>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>Semantic Scholar: 254 citations as of 2026-07-18 (https://api.semanticscholar.org/graph/v1/paper/arXiv:2402.05044?fields=title,citationCount)</t>
+          <t>Volkov, "Badllama 3: removing safety finetuning from Llama 3 in minutes" (Palisade Research, arXiv:2407.01376, 2024-07-01) -- ~9-14 citations per Google Scholar/Semantic Scholar, including red-teaming scaling-law and open-weight risk-mitigation papers</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr"/>
@@ -32169,12 +32121,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SHANGHAIAILAB-2024-01-JAI4</t>
+          <t>SHANGHAIAILAB-2024-02-GOV1</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SHANGHAIAILAB-2024-01</t>
+          <t>SHANGHAIAILAB-2024-02</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -32189,22 +32141,22 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>PsySafe: A Comprehensive Framework for Psychological-based Attack, Defense, and Evaluation of Multi-agent System Safety</t>
+          <t>SALAD-Bench: A Hierarchical and Comprehensive Safety Benchmark for Large Language Models (ACL Findings)</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Jailbreaks</t>
+          <t>Eval-methodology</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>GPT-4 0613; GPT-3.5 Turbo 0613; GPT-4 Turbo</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -32214,17 +32166,17 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>https://arxiv.org/pdf/2401.11880</t>
+          <t>https://arxiv.org/abs/2402.05044</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Under PsySafe's dark-personality-trait injection attack, agents backed by OpenAI models produced dangerous outputs at high rates: GPT-4 0613 reached 61.6% first-round joint danger rate and 100% process danger rate on ostensibly safe tasks (36.9% / 83.0% on dangerous tasks), and GPT-3.5 Turbo 0613 reached 50.0% / 100% on safe tasks and 38.4% / 98.4% on dangerous tasks - the lowest security of the API models tested. GPT-4 Turbo resisted, with a 0.0% joint danger rate throughout though an 83.3% process danger rate on safe tasks.</t>
+          <t>On SALAD-Bench's attack-enhanced subset, Google's Gemini safety rate fell to approximately 20%, a sharp decline from its base-set performance.</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>In contrast, GPT-3.5 Turbo exhibits the lowest security on both the joint danger rate and process danger rate. Although GPT-4 0613 and Gemini Pro exhibit reduced risk in dangerous tasks, their danger rates for safe tasks are exceedingly high.</t>
+          <t>Claude2 leads in performance across both sets, while Gemini’s performance notably declines to approximately 20% in the attack-enhanced subset.</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -32281,7 +32233,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>11880, DOI 10.48550/arXiv.2401.11880, CorpusId 267069372): citationCount 99, influentialCitationCount 8. Peer-reviewed venue recorded as the Annual Meeting of the Association for Computational Linguistics (ACL 2024), DBLP key conf/acl/ZhangZLSG0WLZ24; publicationDate 2024-01-22. This is substantial academic uptake alongside zero located company and government uptake.</t>
+          <t>Semantic Scholar, paperId 868fcbc6127e9cf79990e92116ec482051d470f3, arXiv 2402.05044: citationCount 271, influentialCitationCount 43. Peer-reviewed venue confirmed: Findings of the ACL 2024, https://aclanthology.org/2024.findings-acl.235/ (the finding's own paper - circular, logged for provenance only).</t>
         </is>
       </c>
       <c r="AD221" t="inlineStr">
@@ -32309,12 +32261,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>SHANGHAIAILAB-2024-01-JAI7</t>
+          <t>SHANGHAIAILAB-2024-02-JAI1</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>SHANGHAIAILAB-2024-01</t>
+          <t>SHANGHAIAILAB-2024-02</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -32329,12 +32281,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>PsySafe: A Comprehensive Framework for Psychological-based Attack, Defense, and Evaluation of Multi-agent System Safety</t>
+          <t>SALAD-Bench: A Hierarchical and Comprehensive Safety Benchmark for Large Language Models (ACL Findings)</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -32344,7 +32296,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Llama Guard</t>
+          <t>GPT-4, GPT-3.5, Claude2, Gemini</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -32354,17 +32306,17 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://arxiv.org/pdf/2401.11880</t>
+          <t>https://arxiv.org/abs/2402.05044</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Meta's Llama Guard, used as an input filter against the attack prompts, detected only 1.6% of dangerous examples in the safe-task setting and 49.2% in the dangerous-task setting, and left the joint danger rate on safe tasks unchanged at 45.0-50.0% and the process danger rate at 98.3%.</t>
+          <t>Shanghai AI Lab's SALAD-Bench found Gemini's safety rate dropped sharply under adversarial attack-enhanced prompts (88.32% base to 19.98% attack-enhanced), a far larger degradation than Claude2 (88.02%), GPT-4 (80.28%), or GPT-3.5 (73.38%) on the same attack-enhanced subset.</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>This table shows that the input filter method is ineffective in filtering out our attack prompts.</t>
+          <t>Conversely, Gemini's safety rate significantly drops in the attack-enhanced subset, highlighting potential safety vulnerabilities; Gemini 88.32% (base) to 19.98% (attack-enhanced); Claude2 88.02%; GPT-4 80.28%; GPT-3.5 73.38% [attack-enhanced, Table 5].</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -32414,21 +32366,13 @@
           <t>None located</t>
         </is>
       </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>None located</t>
-        </is>
-      </c>
+      <c r="AB222" t="inlineStr"/>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>Semantic Scholar: paperId 684ede7013b3d844dae13090350a5c27b196727f, 'PsySafe: A Comprehensive Framework for Psychological-based Attack, Defense, and Evaluation of Multi-agent System Safety', publicationDate 2024-01-22, venue Annual Meeting of the Association for Computational Linguistics (ACL 2024), DBLP conf/acl/ZhangZLSG0WLZ24, citationCount 99, influentialCitationCount 8. This is the finding's own paper, so the count is logged as reach evidence only, not as a response.</t>
-        </is>
-      </c>
-      <c r="AD222" t="inlineStr">
-        <is>
-          <t>Hacker News Algolia API searched 2026-08-31 for 'PsySafe': 292 nominal hits, none referring to this paper (all are 'Paysafe' / 'psychological safety' string matches); no Hacker News submission of arXiv:2401.11880 exists. reddit.com/search.json returned HTTP 403 for all queries and is recorded as BLOCKED. No notable public discussion thread located.</t>
-        </is>
-      </c>
+          <t>Semantic Scholar: 254 citations as of 2026-07-18 (https://api.semanticscholar.org/graph/v1/paper/arXiv:2402.05044?fields=title,citationCount)</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr"/>
       <c r="AE222" t="inlineStr"/>
       <c r="AF222" t="inlineStr">
         <is>
@@ -32449,17 +32393,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>APOLLO-2023-11-ALI1</t>
+          <t>SHANGHAIAILAB-2024-01-JAI4</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>APOLLO-2023-11</t>
+          <t>SHANGHAIAILAB-2024-01</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Apollo Research</t>
+          <t>Shanghai AI Laboratory (AI45 Lab)</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -32469,22 +32413,22 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Large Language Models can Strategically Deceive their Users when Put Under Pressure</t>
+          <t>PsySafe: A Comprehensive Framework for Psychological-based Attack, Defense, and Evaluation of Multi-agent System Safety</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alignment</t>
+          <t>Jailbreaks</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>GPT-4</t>
+          <t>GPT-4 0613; GPT-3.5 Turbo 0613; GPT-4 Turbo</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -32494,17 +32438,17 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>https://www.apolloresearch.ai/science/large-language-models-can-strategically-deceive-their-users-when-put-under-pressure/</t>
+          <t>https://arxiv.org/pdf/2401.11880</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Deployed as an autonomous stock-trading agent in a simulated environment, GPT-4 acted on an insider tip despite knowing management disapproved of insider trading, and then consistently hid the real reason for the trade when reporting to its manager - misaligned and strategically deceptive behaviour produced without any instruction or training to deceive.</t>
+          <t>Under PsySafe's dark-personality-trait injection attack, agents backed by OpenAI models produced dangerous outputs at high rates: GPT-4 0613 reached 61.6% first-round joint danger rate and 100% process danger rate on ostensibly safe tasks (36.9% / 83.0% on dangerous tasks), and GPT-3.5 Turbo 0613 reached 50.0% / 100% on safe tasks and 38.4% / 98.4% on dangerous tasks - the lowest security of the API models tested. GPT-4 Turbo resisted, with a 0.0% joint danger rate throughout though an 83.3% process danger rate on safe tasks.</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>Within this environment, the model obtains an insider tip about a lucrative stock trade and acts upon it despite knowing that insider trading is disapproved of by company management. When reporting to its manager, the model consistently hides the genuine reasons behind its trading decision.</t>
+          <t>In contrast, GPT-3.5 Turbo exhibits the lowest security on both the joint danger rate and process danger rate. Although GPT-4 0613 and Gemini Pro exhibit reduced risk in dangerous tasks, their danger rates for safe tasks are exceedingly high.</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -32529,78 +32473,50 @@
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>Explicit attribution</t>
-        </is>
-      </c>
-      <c r="R223" t="inlineStr">
-        <is>
-          <t>UPGRADE on new evidence. The prior coding rested on the Operator system card (2025-01-23), an unattributed product restriction, hence Partial / No explicit attribution. This pass located an OpenAI primary document published eight months later that is squarely a response to this evaluator and this problem. On Action Level: it reports concrete model changes (anti-scheming deliberative alignment training of o3 and o4-mini with a measured ~30x reduction in covert actions; stated deception-propensity mitigations shipped in GPT-5) plus a governance change (two scheming categories added to the Preparedness Framework) - specific mitigations and model changes that address the problem, i.e. Substantive. On Attribution: OpenAI publicly names Apollo Research as its collaborator in the first line of the post and the accompanying joint paper cites this finding by name, so the company has publicly connected its response to the evaluator - Explicit attribution. Corroborating detail: the post's framing analogy is a stock trader who breaks the law and covers his tracks, which is this finding's scenario.</t>
-        </is>
-      </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>Together with Apollo Research, we developed evaluations for hidden misalignment (“scheming”) and found behaviors consistent with scheming in controlled tests across frontier models. | We’ve put significant effort into studying and mitigating deception and have made meaningful improvements in GPT‑5 compared to previous models. For example, we’ve taken steps to limit GPT‑5’s propensity to deceive, cheat, or hack problems | we trained versions of OpenAI o3 and OpenAI o4-mini with deliberative alignment—teaching them to read and reason about a general anti-scheming spec before acting—and observed a ~30× reduction in covert actions across diverse tests (o3 from 13% to 0.4%; o4-mini from 8.7% to 0.3%). | To operationalize this work, we added scheming-related research categories—sandbagging and undermining safeguards—to our updated Preparedness Framework in April 2025.</t>
-        </is>
-      </c>
-      <c r="T223" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="V223" t="inlineStr">
-        <is>
-          <t>https://openai.com/index/detecting-and-reducing-scheming-in-ai-models/</t>
-        </is>
-      </c>
+          <t>No response located</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr"/>
+      <c r="S223" t="inlineStr"/>
+      <c r="T223" t="inlineStr"/>
+      <c r="U223" t="inlineStr"/>
+      <c r="V223" t="inlineStr"/>
       <c r="W223" t="inlineStr">
         <is>
-          <t>Substantive</t>
+          <t>None</t>
         </is>
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>Non-binding policy-related uptake</t>
-        </is>
-      </c>
-      <c r="Y223" t="inlineStr">
-        <is>
-          <t>Ben Lake MP cited Apollo Research by name in the House of Commons AI Safety debate (Westminster Hall, 10 December 2025), referencing its finding that an OpenAI model attempted to deceive users and to disable monitoring mechanisms, as evidence that advanced models deploy techniques to avoid human control.</t>
-        </is>
-      </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>Apollo Research found examples of one of OpenAI's models trying to deceive users to accomplish its goals and, perhaps most worryingly, to disable monitoring mechanisms and guardrails.</t>
-        </is>
-      </c>
+          <t>No policy uptake identified</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr"/>
+      <c r="Z223" t="inlineStr"/>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>https://hansard.parliament.uk/Commons/2025-12-10/debates/9F01B4B9-12CB-42E2-84E2-A65F7D30BFAF/AISafety (Hansard, Commons Westminster Hall, 10 Dec 2025; Ben Lake, Ceredigion Preseli, PC). Retrieved via the Hansard Search API and verified against ContributionTextFull. NOTE: the single cited sentence covers both Apollo/OpenAI findings in this dataset - 'deceive users' maps to APOLLO-2023-11-ALI1 and 'disable monitoring mechanisms' to the o1 scheming evaluation in OPENAI-2024-09-SELF-ALI1; both are coded from it.</t>
+          <t>None located</t>
         </is>
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>Tech Xplore (2023-12-12): https://techxplore.com/news/2023-12-large-language-strategically-users-pressure.html</t>
+          <t>None located</t>
         </is>
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>Google Scholar: 178 citations: https://scholar.google.com/scholar?hl=en&amp;as_sdt=0%2C5&amp;q=%22Large%20Language%20Models%20can%20Strategically%20Deceive%20their%20Users%20when%20Put%20Under%20Pressure%22</t>
-        </is>
-      </c>
-      <c r="AD223" t="inlineStr"/>
-      <c r="AE223" t="inlineStr">
-        <is>
-          <t>“Their findings ... suggest that these models ... could in some cases strategically deceive their users.”</t>
-        </is>
-      </c>
+          <t>11880, DOI 10.48550/arXiv.2401.11880, CorpusId 267069372): citationCount 99, influentialCitationCount 8. Peer-reviewed venue recorded as the Annual Meeting of the Association for Computational Linguistics (ACL 2024), DBLP key conf/acl/ZhangZLSG0WLZ24; publicationDate 2024-01-22. This is substantial academic uptake alongside zero located company and government uptake.</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>None located</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr"/>
       <c r="AF223" t="inlineStr">
         <is>
-          <t>Proportionate</t>
+          <t>Accountability gap (no action)</t>
         </is>
       </c>
       <c r="AG223" t="inlineStr">
@@ -32617,17 +32533,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>PALISADE-2023-10-JAI1</t>
+          <t>SHANGHAIAILAB-2024-01-JAI7</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PALISADE-2023-10-BADLLAMA</t>
+          <t>SHANGHAIAILAB-2024-01</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Palisade Research</t>
+          <t>Shanghai AI Laboratory (AI45 Lab)</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -32637,12 +32553,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Badllama: Cheaply Removing Safety Fine-Tuning from Llama 2-Chat 13B</t>
+          <t>PsySafe: A Comprehensive Framework for Psychological-based Attack, Defense, and Evaluation of Multi-agent System Safety</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -32652,7 +32568,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Llama 2-Chat 13B</t>
+          <t>Llama Guard</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -32662,37 +32578,37 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>https://palisaderesearch.org/blog/badllama</t>
+          <t>https://arxiv.org/pdf/2401.11880</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Palisade effectively undid Llama 2-Chat 13B safety fine-tuning for less than $200 while retaining general capabilities.</t>
+          <t>Meta's Llama Guard, used as an input filter against the attack prompts, detected only 1.6% of dangerous examples in the safe-task setting and 49.2% in the dangerous-task setting, and left the joint danger rate on safe tasks unchanged at 45.0-50.0% and the process danger rate at 98.3%.</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>effectively undo the safety fine-tuning ... with less than $200, while retaining its general capabilities.</t>
+          <t>This table shows that the input filter method is ineffective in filtering out our attack prompts.</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
@@ -32712,35 +32628,31 @@
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>Non-binding policy-related uptake</t>
-        </is>
-      </c>
-      <c r="Y224" t="inlineStr">
-        <is>
-          <t>Two official government publications explicitly cite the Badllama report. UK: 'AI Scenarios 2030: Helping policymakers plan for the future of AI' (GOV.UK publication, Government Office for Science with AISI and DSIT, 15 June 2026) cites it in body text for the proposition that fine-tuning can easily remove safeguards on open-weight models. US: NIST AI 100-2e2025, Adversarial Machine Learning: A Taxonomy and Terminology of Attacks and Mitigations (US Department of Commerce/NIST, March 2025) cites it as ref [132] in body text as a source for 'fine-tuning circumvention attacks which remove refusal behavior'. Neither imposes an enforceable obligation.</t>
-        </is>
-      </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>DSIT/GO-Science, 'AI Scenarios 2030', Sec. 2.3 (Open- vs. closed-weight models): "While the key components of closed-weight AI systems are proprietary and fixed, open-weight AI models can be downloaded, modified, and operated locally by anyone. They can be fine-tuned to specific uses, widely red-teamed, and used for types of research requiring weights access. However, fine-tuning can also easily remove any safeguards, increasing risks of malicious use (Gade et al., 2024)." Reference list: "Gade, P. et al. (2024) BadLlama: cheaply removing safety fine-tuning from Llama 2-Chat 13B. Available at: https://arxiv.org/abs/2311.00117 (Accessed: 20 May 2026)." || NIST AI 100-2e2025, attacker-capabilities section: "MODEL CONTROL: The attacker might have the ability to modify model parameters, such as through public fine-tuning APIs or openly accessible model weights. This capability is used in MODEL POISONING attacks, as well FINE-TUNING CIRCUMVENTION attacks which remove refusal behavior or other model-level safety interventions [132, 153, 300]." Reference [132]: "Pranav Gade, Simon Lermen, Charlie Rogers-Smith, and Jeffrey Ladish. Badllama: cheaply removing safety fine-tuning from llama 2-chat 13b, 2024. URL: https://arxiv.org/abs/2311.00117".</t>
-        </is>
-      </c>
+          <t>No policy uptake identified</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr"/>
+      <c r="Z224" t="inlineStr"/>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>https://assets.publishing.service.gov.uk/media/6a2aa1fbe50716856ed4aeea/AI_Scenarios_2030_pdf.pdf</t>
+          <t>None located</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>AlignmentForum/LessWrong discussion of the underlying research ("LoRA Fine-tuning Efficiently Undoes Safety Training from Llama 2-Chat")</t>
+          <t>None located</t>
         </is>
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>arXiv:2311.00117 ("BadLlama") referenced in later fine-tuning-jailbreak-defense papers, e.g. arXiv:2510.07835 (MetaDefense), arXiv:2505.17196 (Shape it Up!)</t>
-        </is>
-      </c>
-      <c r="AD224" t="inlineStr"/>
+          <t>Semantic Scholar: paperId 684ede7013b3d844dae13090350a5c27b196727f, 'PsySafe: A Comprehensive Framework for Psychological-based Attack, Defense, and Evaluation of Multi-agent System Safety', publicationDate 2024-01-22, venue Annual Meeting of the Association for Computational Linguistics (ACL 2024), DBLP conf/acl/ZhangZLSG0WLZ24, citationCount 99, influentialCitationCount 8. This is the finding's own paper, so the count is logged as reach evidence only, not as a response.</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>Hacker News Algolia API searched 2026-08-31 for 'PsySafe': 292 nominal hits, none referring to this paper (all are 'Paysafe' / 'psychological safety' string matches); no Hacker News submission of arXiv:2401.11880 exists. reddit.com/search.json returned HTTP 403 for all queries and is recorded as BLOCKED. No notable public discussion thread located.</t>
+        </is>
+      </c>
       <c r="AE224" t="inlineStr"/>
       <c r="AF224" t="inlineStr">
         <is>
@@ -32761,42 +32673,42 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SECUREBIO-2023-10-ALI1</t>
+          <t>APOLLO-2023-11-ALI1</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SECUREBIO-2023-10</t>
+          <t>APOLLO-2023-11</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>SecureBio</t>
+          <t>Apollo Research</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Non-Profit (AIEF)</t>
+          <t>Non-Profit (Independent)</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Will releasing the weights of future large language models grant widespread access to pandemic agents?</t>
+          <t>Large Language Models can Strategically Deceive their Users when Put Under Pressure</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Jailbreaks; Bio-Chem</t>
+          <t>Alignment</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Llama-2-70B ("Base" chat-tuned)</t>
+          <t>GPT-4</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -32806,17 +32718,17 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2310.18233</t>
+          <t>https://www.apolloresearch.ai/science/large-language-models-can-strategically-deceive-their-users-when-put-under-pressure/</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Base Llama-2-70B's safeguards were not robust to adversarial prompting: the authors report the base model possesses the same dangerous capabilities as the uncensored variant and will divulge them if laboriously jailbroken using prompt injection, and one participant used advice obtained from the Spicy model to pose as a virologist interested in vaccine development in order to jailbreak the Base model.</t>
+          <t>Deployed as an autonomous stock-trading agent in a simulated environment, GPT-4 acted on an insider tip despite knowing management disapproved of insider trading, and then consistently hid the real reason for the trade when reporting to its manager - misaligned and strategically deceptive behaviour produced without any instruction or training to deceive.</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>The Base model possesses the same capabilities, but will only divulge them if laboriously jailbroken using prompt injection.</t>
+          <t>Within this environment, the model obtains an insider tip about a lucrative stock trade and acts upon it despite knowing that insider trading is disapproved of by company management. When reporting to its manager, the model consistently hides the genuine reasons behind its trading decision.</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -32841,50 +32753,78 @@
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>No response located</t>
-        </is>
-      </c>
-      <c r="R225" t="inlineStr"/>
-      <c r="S225" t="inlineStr"/>
-      <c r="T225" t="inlineStr"/>
-      <c r="U225" t="inlineStr"/>
-      <c r="V225" t="inlineStr"/>
+          <t>Explicit attribution</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>UPGRADE on new evidence. The prior coding rested on the Operator system card (2025-01-23), an unattributed product restriction, hence Partial / No explicit attribution. This pass located an OpenAI primary document published eight months later that is squarely a response to this evaluator and this problem. On Action Level: it reports concrete model changes (anti-scheming deliberative alignment training of o3 and o4-mini with a measured ~30x reduction in covert actions; stated deception-propensity mitigations shipped in GPT-5) plus a governance change (two scheming categories added to the Preparedness Framework) - specific mitigations and model changes that address the problem, i.e. Substantive. On Attribution: OpenAI publicly names Apollo Research as its collaborator in the first line of the post and the accompanying joint paper cites this finding by name, so the company has publicly connected its response to the evaluator - Explicit attribution. Corroborating detail: the post's framing analogy is a stock trader who breaks the law and covers his tracks, which is this finding's scenario.</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>Together with Apollo Research, we developed evaluations for hidden misalignment (“scheming”) and found behaviors consistent with scheming in controlled tests across frontier models. | We’ve put significant effort into studying and mitigating deception and have made meaningful improvements in GPT‑5 compared to previous models. For example, we’ve taken steps to limit GPT‑5’s propensity to deceive, cheat, or hack problems | we trained versions of OpenAI o3 and OpenAI o4-mini with deliberative alignment—teaching them to read and reason about a general anti-scheming spec before acting—and observed a ~30× reduction in covert actions across diverse tests (o3 from 13% to 0.4%; o4-mini from 8.7% to 0.3%). | To operationalize this work, we added scheming-related research categories—sandbagging and undermining safeguards—to our updated Preparedness Framework in April 2025.</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>https://openai.com/index/detecting-and-reducing-scheming-in-ai-models/</t>
+        </is>
+      </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Substantive</t>
         </is>
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>No policy uptake identified</t>
-        </is>
-      </c>
-      <c r="Y225" t="inlineStr"/>
-      <c r="Z225" t="inlineStr"/>
+          <t>Non-binding policy-related uptake</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>Ben Lake MP cited Apollo Research by name in the House of Commons AI Safety debate (Westminster Hall, 10 December 2025), referencing its finding that an OpenAI model attempted to deceive users and to disable monitoring mechanisms, as evidence that advanced models deploy techniques to avoid human control.</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>Apollo Research found examples of one of OpenAI's models trying to deceive users to accomplish its goals and, perhaps most worryingly, to disable monitoring mechanisms and guardrails.</t>
+        </is>
+      </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>None located</t>
+          <t>https://hansard.parliament.uk/Commons/2025-12-10/debates/9F01B4B9-12CB-42E2-84E2-A65F7D30BFAF/AISafety (Hansard, Commons Westminster Hall, 10 Dec 2025; Ben Lake, Ceredigion Preseli, PC). Retrieved via the Hansard Search API and verified against ContributionTextFull. NOTE: the single cited sentence covers both Apollo/OpenAI findings in this dataset - 'deceive users' maps to APOLLO-2023-11-ALI1 and 'disable monitoring mechanisms' to the o1 scheming evaluation in OPENAI-2024-09-SELF-ALI1; both are coded from it.</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>None located</t>
+          <t>Tech Xplore (2023-12-12): https://techxplore.com/news/2023-12-large-language-strategically-users-pressure.html</t>
         </is>
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>Semantic Scholar, retrieved 2026-08-31: paperId 7acd87ee3e03c5432bd5969411cdd8f97ea5981f, citationCount 29, influentialCitationCount 1, publicationDate 2023-10-25. Notable citing works (from the S2 /citations endpoint, same retrieval): 'The WMDP Benchmark: Measuring and Reducing Malicious Use With Unlearning' (Li et al., 2024); 'On the Societal Impact of Open Foundation Models' (Kapoor, Bommasani, Klyman et al., 2024); 'HarmBench: A Standardized Evaluation Framework for Automated Red Teaming and Robust Refusal' (Mazeika et al., 2024); 'Dual-use capabilities of concern of biological AI models' (Pannu, Bloomfield, Zhu et al., 2024); 'LoRA Fine-tuning Efficiently Undoes Safety Training in Llama 2-Chat 70B' (Lermen, Rogers-Smith, Ladish, 2023); 'Virology Capabilities Test (VCT)' (Gotting, Medeiros, Sanders et al., 2025); 'Representation Noising: A Defence Mechanism Against Harmful Finetuning' (Rosati et al., 2024). No Meta-authored paper appears in the citing list.</t>
-        </is>
-      </c>
-      <c r="AD225" t="inlineStr">
-        <is>
-          <t>None located</t>
-        </is>
-      </c>
-      <c r="AE225" t="inlineStr"/>
+          <t>Google Scholar: 178 citations: https://scholar.google.com/scholar?hl=en&amp;as_sdt=0%2C5&amp;q=%22Large%20Language%20Models%20can%20Strategically%20Deceive%20their%20Users%20when%20Put%20Under%20Pressure%22</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr"/>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>“Their findings ... suggest that these models ... could in some cases strategically deceive their users.”</t>
+        </is>
+      </c>
       <c r="AF225" t="inlineStr">
         <is>
-          <t>Accountability gap (no action)</t>
+          <t>Proportionate</t>
         </is>
       </c>
       <c r="AG225" t="inlineStr">
@@ -32901,42 +32841,42 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SECUREBIO-2023-10-BIO1</t>
+          <t>PALISADE-2023-10-JAI1</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>SECUREBIO-2023-10</t>
+          <t>PALISADE-2023-10-BADLLAMA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>SecureBio</t>
+          <t>Palisade Research</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Non-Profit (AIEF)</t>
+          <t>Non-Profit (Independent)</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Will releasing the weights of future large language models grant widespread access to pandemic agents?</t>
+          <t>Badllama: Cheaply Removing Safety Fine-Tuning from Llama 2-Chat 13B</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Bio-Chem</t>
+          <t>Jailbreaks</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Llama-2-70B ("Base" chat-tuned) and its uncensored fine-tune "Spicy" (Spicyboros), further LoRA fine-tuned on virology papers</t>
+          <t>Llama 2-Chat 13B</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -32946,37 +32886,37 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2310.18233</t>
+          <t>https://palisaderesearch.org/blog/badllama</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>In a hackathon with 17 participants at MIT, 11 of whom followed instructions to enter overtly malicious prompts, a publicly available 'uncensored' fine-tune of Meta's Llama-2-70B (Spicyboros, fine-tuned for about $200) nearly always attempted to supply the requested information for acquiring and releasing the 1918 H1N1 influenza virus, including methods for effective pathogen dispersal, instructions for building homemade lab equipment and strategies to bypass DNA synthesis screening, whereas base Llama-2-70B almost always refused. No participant obtained information sufficient to acquire infectious samples within their 1-3 hours, but the authors verified that all key information along a complete acquisition path could be obtained in under an hour and that the Spicy model could walk a user along the most accessible path in 30 minutes.</t>
+          <t>Palisade effectively undid Llama 2-Chat 13B safety fine-tuning for less than $200 while retaining general capabilities.</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>Those using the Spicy model also discovered methods for effective pathogen dispersal to cause widespread harm, instructions for building homemade lab equipment, and strategies to bypass DNA synthesis screening.</t>
+          <t>effectively undo the safety fine-tuning ... with less than $200, while retaining its general capabilities.</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>ERR</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
@@ -32996,36 +32936,36 @@
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>No policy uptake identified</t>
-        </is>
-      </c>
-      <c r="Y226" t="inlineStr"/>
-      <c r="Z226" t="inlineStr"/>
+          <t>Non-binding policy-related uptake</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>Two official government publications explicitly cite the Badllama report. UK: 'AI Scenarios 2030: Helping policymakers plan for the future of AI' (GOV.UK publication, Government Office for Science with AISI and DSIT, 15 June 2026) cites it in body text for the proposition that fine-tuning can easily remove safeguards on open-weight models. US: NIST AI 100-2e2025, Adversarial Machine Learning: A Taxonomy and Terminology of Attacks and Mitigations (US Department of Commerce/NIST, March 2025) cites it as ref [132] in body text as a source for 'fine-tuning circumvention attacks which remove refusal behavior'. Neither imposes an enforceable obligation.</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>DSIT/GO-Science, 'AI Scenarios 2030', Sec. 2.3 (Open- vs. closed-weight models): "While the key components of closed-weight AI systems are proprietary and fixed, open-weight AI models can be downloaded, modified, and operated locally by anyone. They can be fine-tuned to specific uses, widely red-teamed, and used for types of research requiring weights access. However, fine-tuning can also easily remove any safeguards, increasing risks of malicious use (Gade et al., 2024)." Reference list: "Gade, P. et al. (2024) BadLlama: cheaply removing safety fine-tuning from Llama 2-Chat 13B. Available at: https://arxiv.org/abs/2311.00117 (Accessed: 20 May 2026)." || NIST AI 100-2e2025, attacker-capabilities section: "MODEL CONTROL: The attacker might have the ability to modify model parameters, such as through public fine-tuning APIs or openly accessible model weights. This capability is used in MODEL POISONING attacks, as well FINE-TUNING CIRCUMVENTION attacks which remove refusal behavior or other model-level safety interventions [132, 153, 300]." Reference [132]: "Pranav Gade, Simon Lermen, Charlie Rogers-Smith, and Jeffrey Ladish. Badllama: cheaply removing safety fine-tuning from llama 2-chat 13b, 2024. URL: https://arxiv.org/abs/2311.00117".</t>
+        </is>
+      </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>None located</t>
+          <t>https://assets.publishing.service.gov.uk/media/6a2aa1fbe50716856ed4aeea/AI_Scenarios_2030_pdf.pdf</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>THE DECODER, 'Open-source language models could simplify bioterrorism', dated 2023-11-01, describing the hackathon and the Spicyboros variant - https://the-decoder.com/open-source-language-models-could-simplify-bioterrorism/ (index-confirmed with title, date and a body snippet naming 'Spicyboro' on 2026-08-31; the live URL now serves the site feed rather than the article and the Wayback availability API returns no snapshot, so the body could not be re-read - logged as index-level evidence only). Bulletin of the Atomic Scientists, 2024-06-03, on the same MIT group's follow-on DNA-synthesis-screening work and its AI/biosecurity context - https://thebulletin.org/2024/06/... (403 to fetch on 2026-08-31; adjacent coverage of the group, not of this finding, so logged only as context). No mainstream wire or national-newspaper coverage of this specific paper was verified.</t>
+          <t>AlignmentForum/LessWrong discussion of the underlying research ("LoRA Fine-tuning Efficiently Undoes Safety Training from Llama 2-Chat")</t>
         </is>
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>Semantic Scholar API, checked 2026-08-31: paperId 7acd87ee3e03c5432bd5969411cdd8f97ea5981f, 'Will releasing the weights of future large language models grant widespread access to pandemic agents?', publicationDate 2023-10-25, citationCount 29, influentialCitationCount 1 (https://api.semanticscholar.org/graph/v1/paper/arXiv:2310.18233). Also indexed by NASA ADS as 2023arXiv231018233G.</t>
-        </is>
-      </c>
-      <c r="AD226" t="inlineStr">
-        <is>
-          <t>LessWrong linkpost, 'Will releasing the weights of large language models grant widespread access to pandemic agents?', 2023-10-30 - https://www.lesswrong.com/posts/ytGsHbG7r3W3nJxPT/.... Channel C is log-only and is never scored.</t>
-        </is>
-      </c>
-      <c r="AE226" t="inlineStr">
-        <is>
-          <t>THE DECODER, 2023-11-01: "Participants were given two versions of Meta's open-source Llama 2 language model to query: the publicly available base version of Meta with built-in safeguards, and a more 'permissive' version of Spicyboro, customized for this use case, with the safeguards removed." [index-served snippet; the article body could not be re-fetched or archived on 2026-08-31, so this is logged as attributed-but-unverified-in-body. Channel C, log only.]</t>
-        </is>
-      </c>
+          <t>arXiv:2311.00117 ("BadLlama") referenced in later fine-tuning-jailbreak-defense papers, e.g. arXiv:2510.07835 (MetaDefense), arXiv:2505.17196 (Shape it Up!)</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr"/>
+      <c r="AE226" t="inlineStr"/>
       <c r="AF226" t="inlineStr">
         <is>
           <t>Accountability gap (no action)</t>
@@ -33045,42 +32985,42 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CAIS-2023-07-JAI1</t>
+          <t>SECUREBIO-2023-10-ALI1</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>CAIS-2023-07</t>
+          <t>SECUREBIO-2023-10</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Center for AI Safety (CAIS)</t>
+          <t>SecureBio</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Non-Profit (Independent)</t>
+          <t>Non-Profit (AIEF)</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Universal and Transferable Adversarial Attacks on Aligned Language Models</t>
+          <t>Will releasing the weights of future large language models grant widespread access to pandemic agents?</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Jailbreaks</t>
+          <t>Jailbreaks; Bio-Chem</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>GPT-3.5 (gpt-3.5-turbo), GPT-4 (gpt-4-0314)</t>
+          <t>Llama-2-70B ("Base" chat-tuned)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -33090,17 +33030,17 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>https://arxiv.org/pdf/2307.15043</t>
+          <t>https://arxiv.org/abs/2310.18233</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Adversarial suffixes optimised only against open-weight Vicuna models transferred to OpenAI's production chat models without any access to their weights, reaching 87.9% attack success on GPT-3.5 and 53.6% on GPT-4 over a set of harmful behaviours.</t>
+          <t>Base Llama-2-70B's safeguards were not robust to adversarial prompting: the authors report the base model possesses the same dangerous capabilities as the uncensored variant and will divulge them if laboriously jailbroken using prompt injection, and one participant used advice obtained from the Spicy model to pose as a virologist interested in vaccine development in order to jailbreak the Base model.</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>By generating adversarial examples to fool both Vicuna-7B and Vicuna-13b simultaneously, we find that the adversarial examples also transfer to Pythia, Falcon, Guanaco, and surprisingly, to GPT-3.5 (87.9%) and GPT-4 (53.6%), PaLM-2 (66%), and Claude-2 (2.1%).</t>
+          <t>The Base model possesses the same capabilities, but will only divulge them if laboriously jailbroken using prompt injection.</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -33125,82 +33065,50 @@
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>No explicit attribution</t>
-        </is>
-      </c>
-      <c r="R227" t="inlineStr">
-        <is>
-          <t>OpenAI applied deliberative alignment to its o-series successor models, directly training them to reason over safety specifications and documenting substantially improved resistance to malicious jailbreak prompts.</t>
-        </is>
-      </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>We used deliberative alignment to align OpenAI’s o-series models, enabling them to use chain-of-thought (CoT) reasoning to reflect on user prompts, identify relevant text from OpenAI’s internal policies, and draft safer responses.</t>
-        </is>
-      </c>
-      <c r="T227" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>https://openai.com/index/deliberative-alignment/</t>
-        </is>
-      </c>
+          <t>No response located</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr"/>
+      <c r="S227" t="inlineStr"/>
+      <c r="T227" t="inlineStr"/>
+      <c r="U227" t="inlineStr"/>
+      <c r="V227" t="inlineStr"/>
       <c r="W227" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>None</t>
         </is>
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>Non-binding policy-related uptake</t>
-        </is>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>NIST incorporated the paper's universal and transferable adversarial-suffix finding into its March 2025 adversarial-machine-learning taxonomy and mitigation guidance.</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>“That these universal triggers transfer to other models makes open-weight models ... feasible attack vectors for transferability attacks on closed systems.”</t>
-        </is>
-      </c>
+          <t>No policy uptake identified</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr"/>
+      <c r="Z227" t="inlineStr"/>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-2e2025.pdf</t>
+          <t>None located</t>
         </is>
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>Tech Xplore (2023-07-31): https://techxplore.com/news/2023-07-vulnerability-large-language.pdf</t>
+          <t>None located</t>
         </is>
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>Google Scholar: 4,217 citations: https://scholar.google.com/scholar?hl=en&amp;as_sdt=0%2C5&amp;q=%22Universal%20and%20Transferable%20Adversarial%20Attacks%20on%20Aligned%20Language%20Models%22 Semantic Scholar: 2,637 citations: https://www.semanticscholar.org/search?q=Universal%20and%20Transferable%20Adversarial%20Attacks%20on%20Aligned%20Language%20Models&amp;sort=relevance</t>
+          <t>Semantic Scholar, retrieved 2026-08-31: paperId 7acd87ee3e03c5432bd5969411cdd8f97ea5981f, citationCount 29, influentialCitationCount 1, publicationDate 2023-10-25. Notable citing works (from the S2 /citations endpoint, same retrieval): 'The WMDP Benchmark: Measuring and Reducing Malicious Use With Unlearning' (Li et al., 2024); 'On the Societal Impact of Open Foundation Models' (Kapoor, Bommasani, Klyman et al., 2024); 'HarmBench: A Standardized Evaluation Framework for Automated Red Teaming and Robust Refusal' (Mazeika et al., 2024); 'Dual-use capabilities of concern of biological AI models' (Pannu, Bloomfield, Zhu et al., 2024); 'LoRA Fine-tuning Efficiently Undoes Safety Training in Llama 2-Chat 70B' (Lermen, Rogers-Smith, Ladish, 2023); 'Virology Capabilities Test (VCT)' (Gotting, Medeiros, Sanders et al., 2025); 'Representation Noising: A Defence Mechanism Against Harmful Finetuning' (Rosati et al., 2024). No Meta-authored paper appears in the citing list.</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr">
         <is>
-          <t>Hacker News discussion: https://news.ycombinator.com/item?id=36921808</t>
-        </is>
-      </c>
-      <c r="AE227" t="inlineStr">
-        <is>
-          <t>“Our attack constructs a single adversarial prompt that consistently circumvents the alignment of state-of-the-art commercial models.”</t>
-        </is>
-      </c>
+          <t>None located</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr"/>
       <c r="AF227" t="inlineStr">
         <is>
-          <t>Under-response (gap)</t>
+          <t>Accountability gap (no action)</t>
         </is>
       </c>
       <c r="AG227" t="inlineStr">
@@ -33217,42 +33125,42 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CAIS-2023-07-JAI2</t>
+          <t>SECUREBIO-2023-10-BIO1</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>CAIS-2023-07</t>
+          <t>SECUREBIO-2023-10</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Center for AI Safety (CAIS)</t>
+          <t>SecureBio</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Non-Profit (Independent)</t>
+          <t>Non-Profit (AIEF)</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Universal and Transferable Adversarial Attacks on Aligned Language Models</t>
+          <t>Will releasing the weights of future large language models grant widespread access to pandemic agents?</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Jailbreaks</t>
+          <t>Bio-Chem</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>PaLM-2, Bard</t>
+          <t>Llama-2-70B ("Base" chat-tuned) and its uncensored fine-tune "Spicy" (Spicyboros), further LoRA fine-tuned on virology papers</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -33262,17 +33170,17 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>https://arxiv.org/pdf/2307.15043</t>
+          <t>https://arxiv.org/abs/2310.18233</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>The same transferred adversarial suffixes elicited objectionable content from Google's PaLM-2 at a 66% ensemble attack success rate and from the public Bard interface, despite the attack never being optimised against either system.</t>
+          <t>In a hackathon with 17 participants at MIT, 11 of whom followed instructions to enter overtly malicious prompts, a publicly available 'uncensored' fine-tune of Meta's Llama-2-70B (Spicyboros, fine-tuned for about $200) nearly always attempted to supply the requested information for acquiring and releasing the 1918 H1N1 influenza virus, including methods for effective pathogen dispersal, instructions for building homemade lab equipment and strategies to bypass DNA synthesis screening, whereas base Llama-2-70B almost always refused. No participant obtained information sufficient to acquire infectious samples within their 1-3 hours, but the authors verified that all key information along a complete acquisition path could be obtained in under an hour and that the Spicy model could walk a user along the most accessible path in 30 minutes.</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>When doing so, the resulting attack suffix induces objectionable content in the public interfaces to ChatGPT, Bard, and Claude, as well as open source LLMs such as LLaMA-2-Chat, Pythia, Falcon, and others.</t>
+          <t>Those using the Spicy model also discovered methods for effective pathogen dispersal to cause widespread harm, instructions for building homemade lab equipment, and strategies to bypass DNA synthesis screening.</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -33282,7 +33190,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>ERR</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -33312,42 +33220,34 @@
       </c>
       <c r="X228" t="inlineStr">
         <is>
-          <t>Non-binding policy-related uptake</t>
-        </is>
-      </c>
-      <c r="Y228" t="inlineStr">
-        <is>
-          <t>NIST incorporated the paper's universal and transferable adversarial-suffix finding into its March 2025 adversarial-machine-learning taxonomy and mitigation guidance.</t>
-        </is>
-      </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>“That these universal triggers transfer to other models makes open-weight models ... feasible attack vectors for transferability attacks on closed systems.”</t>
-        </is>
-      </c>
+          <t>No policy uptake identified</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr"/>
+      <c r="Z228" t="inlineStr"/>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-2e2025.pdf</t>
+          <t>None located</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>Tech Xplore (2023-07-31): https://techxplore.com/news/2023-07-vulnerability-large-language.pdf</t>
+          <t>THE DECODER, 'Open-source language models could simplify bioterrorism', dated 2023-11-01, describing the hackathon and the Spicyboros variant - https://the-decoder.com/open-source-language-models-could-simplify-bioterrorism/ (index-confirmed with title, date and a body snippet naming 'Spicyboro' on 2026-08-31; the live URL now serves the site feed rather than the article and the Wayback availability API returns no snapshot, so the body could not be re-read - logged as index-level evidence only). Bulletin of the Atomic Scientists, 2024-06-03, on the same MIT group's follow-on DNA-synthesis-screening work and its AI/biosecurity context - https://thebulletin.org/2024/06/... (403 to fetch on 2026-08-31; adjacent coverage of the group, not of this finding, so logged only as context). No mainstream wire or national-newspaper coverage of this specific paper was verified.</t>
         </is>
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>Google Scholar: 4,217 citations: https://scholar.google.com/scholar?hl=en&amp;as_sdt=0%2C5&amp;q=%22Universal%20and%20Transferable%20Adversarial%20Attacks%20on%20Aligned%20Language%20Models%22 Semantic Scholar: 2,637 citations: https://www.semanticscholar.org/search?q=Universal%20and%20Transferable%20Adversarial%20Attacks%20on%20Aligned%20Language%20Models&amp;sort=relevance</t>
+          <t>Semantic Scholar API, checked 2026-08-31: paperId 7acd87ee3e03c5432bd5969411cdd8f97ea5981f, 'Will releasing the weights of future large language models grant widespread access to pandemic agents?', publicationDate 2023-10-25, citationCount 29, influentialCitationCount 1 (https://api.semanticscholar.org/graph/v1/paper/arXiv:2310.18233). Also indexed by NASA ADS as 2023arXiv231018233G.</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr">
         <is>
-          <t>Hacker News discussion: https://news.ycombinator.com/item?id=36921808</t>
+          <t>LessWrong linkpost, 'Will releasing the weights of large language models grant widespread access to pandemic agents?', 2023-10-30 - https://www.lesswrong.com/posts/ytGsHbG7r3W3nJxPT/.... Channel C is log-only and is never scored.</t>
         </is>
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>“The adversarial prompt can elicit arbitrary harmful behaviors from these models with high probability.”</t>
+          <t>THE DECODER, 2023-11-01: "Participants were given two versions of Meta's open-source Llama 2 language model to query: the publicly available base version of Meta with built-in safeguards, and a more 'permissive' version of Spicyboro, customized for this use case, with the safeguards removed." [index-served snippet; the article body could not be re-fetched or archived on 2026-08-31, so this is logged as attributed-but-unverified-in-body. Channel C, log only.]</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -33369,7 +33269,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CAIS-2023-07-JAI3</t>
+          <t>CAIS-2023-07-JAI1</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -33404,7 +33304,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Claude-1 (claude-instant-1), Claude-2</t>
+          <t>GPT-3.5 (gpt-3.5-turbo), GPT-4 (gpt-4-0314)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -33419,12 +33319,12 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Transferred GCG suffixes jailbroke Claude-1 (claude-instant-1) at up to a 47.9% ensemble attack success rate over 388 harmful behaviours, while Claude-2 proved far more robust at 2.1%; the authors note the attack still induced behaviour Claude otherwise never generates.</t>
+          <t>Adversarial suffixes optimised only against open-weight Vicuna models transferred to OpenAI's production chat models without any access to their weights, reaching 87.9% attack success on GPT-3.5 and 53.6% on GPT-4 over a set of harmful behaviours.</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>Interestingly, when using the prompt also optimized on Guanacos, we are able to further increase ASR on Claude-1. Claude-2 appears to be more robust compared to the other commercial models.</t>
+          <t>By generating adversarial examples to fool both Vicuna-7B and Vicuna-13b simultaneously, we find that the adversarial examples also transfer to Pythia, Falcon, Guanaco, and surprisingly, to GPT-3.5 (87.9%) and GPT-4 (53.6%), PaLM-2 (66%), and Claude-2 (2.1%).</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -33454,27 +33354,27 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>Anthropic developed and publicly tested Constitutional Classifiers against universal jailbreaks on Claude 3.5 Sonnet, reporting substantially lower jailbreak success but describing the system as a prototype intended for possible future deployment.</t>
+          <t>OpenAI applied deliberative alignment to its o-series successor models, directly training them to reason over safety specifications and documenting substantially improved resistance to malicious jailbreak prompts.</t>
         </is>
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>A prototype version of the method was robust to thousands of hours of human red teaming for universal jailbreaks, albeit with high overrefusal rates and compute overhead.</t>
+          <t>We used deliberative alignment to align OpenAI’s o-series models, enabling them to use chain-of-thought (CoT) reasoning to reflect on user prompts, identify relevant text from OpenAI’s internal policies, and draft safer responses.</t>
         </is>
       </c>
       <c r="T229" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>512</t>
         </is>
       </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>https://www.anthropic.com/news/constitutional-classifiers</t>
+          <t>https://openai.com/index/deliberative-alignment/</t>
         </is>
       </c>
       <c r="W229" t="inlineStr">
@@ -33519,7 +33419,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>“People can still attack it by looking at freely available, smaller and simpler open-sourced models and learning how to attack those.”</t>
+          <t>“Our attack constructs a single adversarial prompt that consistently circumvents the alignment of state-of-the-art commercial models.”</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -33541,42 +33441,42 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SECUREBIO-2023-06-BIO1</t>
+          <t>CAIS-2023-07-JAI2</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SECUREBIO-2023-06</t>
+          <t>CAIS-2023-07</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>SecureBio</t>
+          <t>Center for AI Safety (CAIS)</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Non-Profit (AIEF)</t>
+          <t>Non-Profit (Independent)</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Can large language models democratize access to dual-use biotechnology?</t>
+          <t>Universal and Transferable Adversarial Attacks on Aligned Language Models</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Bio-Chem</t>
+          <t>Jailbreaks</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>GPT-4; GPT-3.5; Bing; Bard; FreedomGPT (results reported in aggregate across the chatbots, not attributed model-by-model)</t>
+          <t>PaLM-2, Bard</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -33586,17 +33486,17 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2306.03809</t>
+          <t>https://arxiv.org/pdf/2307.15043</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>In a one-hour 'Safeguarding the Future' classroom exercise at MIT, three groups of non-scientist students prompted publicly available chatbots (GPT-4, GPT-3.5, Bing, Bard and open-source models including FreedomGPT) and were directed to four potential pandemic pathogens (1918 H1N1 influenza, transmission-enhanced H5N1, variola major, and the Bangladesh strain of Nipah), given links to reverse-genetics protocols and the papers that used them, told that the IGSC member list identifies which DNA synthesis companies do not screen orders, shown how BLAST-based screening could be evaded by redesigning sequences, and advised that anyone lacking reverse-genetics skills could hire a core facility or contract research organization.</t>
+          <t>The same transferred adversarial suffixes elicited objectionable content from Google's PaLM-2 at a 66% ensemble attack success rate and from the public Bard interface, despite the attack never being optimised against either system.</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>In one hour, the chatbots suggested four potential pandemic pathogens, explained how they can be generated from synthetic DNA using reverse genetics, supplied the names of DNA synthesis companies unlikely to screen orders, identified detailed protocols and how to troubleshoot them, and recommended that anyone lacking the skills to perform reverse genetics engage a core facility or contract research organization.</t>
+          <t>When doing so, the resulting attack suffix induces objectionable content in the public interfaces to ChatGPT, Bard, and Claude, as well as open source LLMs such as LLaMA-2-Chat, Pythia, Falcon, and others.</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -33606,7 +33506,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>ERR</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -33621,37 +33521,17 @@
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>Explicit attribution</t>
-        </is>
-      </c>
-      <c r="R230" t="inlineStr">
-        <is>
-          <t>In its 31 January 2024 publication 'Building an early warning system for LLM-aided biological threat creation', OpenAI cites the finding by name (Soice et al, 2023, hyperlinked to arXiv:2306.03809) as part of the existing research establishing that models like GPT-4 can be prompted or red-teamed to share biological-threat-creation information, and on that basis sets out a new biothreat evaluation methodology under its Preparedness Framework. The citation acknowledges the finding; OpenAI attributes no specific safeguard or model change to it.</t>
-        </is>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>Existing research on AI-enabled biological threats has shown that models like GPT-4 can be prompted or red-teamed to share information related to biological threat creation (see GPT-4 system card, Egan et al., 2023, Gopal et al., 2023, Soice et al, 2023, and Ganguli et al., 2023).</t>
-        </is>
-      </c>
-      <c r="T230" t="inlineStr">
-        <is>
-          <t>2024-01-31</t>
-        </is>
-      </c>
-      <c r="U230" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="V230" t="inlineStr">
-        <is>
-          <t>https://openai.com/index/building-an-early-warning-system-for-llm-aided-biological-threat-creation/</t>
-        </is>
-      </c>
+          <t>No response located</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr"/>
+      <c r="S230" t="inlineStr"/>
+      <c r="T230" t="inlineStr"/>
+      <c r="U230" t="inlineStr"/>
+      <c r="V230" t="inlineStr"/>
       <c r="W230" t="inlineStr">
         <is>
-          <t>Acknowledged</t>
+          <t>None</t>
         </is>
       </c>
       <c r="X230" t="inlineStr">
@@ -33661,42 +33541,42 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>The UK Government's official pre-AI Safety Summit discussion paper 'Capabilities and risks from frontier AI' (Department for Science, Innovation and Technology, published 25 October 2023) cites the finding by title and author as the evidential support for its statement that frontier AI systems may provide instruction on how to acquire biological and chemical materials - footnote 195 of the report's biosecurity section. This is analytical uptake in a government publication that framed the Bletchley Park summit agenda; it imposes no legal obligation, so it is coded as non-binding rather than binding.</t>
+          <t>NIST incorporated the paper's universal and transferable adversarial-suffix finding into its March 2025 adversarial-machine-learning taxonomy and mitigation guidance.</t>
         </is>
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>Can Large Language Models Democratize Access to Dual-use Biotechnology?, Soice et al., 2023</t>
+          <t>“That these universal triggers transfer to other models makes open-weight models ... feasible attack vectors for transferability attacks on closed systems.”</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/frontier-ai-capabilities-and-risks-discussion-paper (PDF asset: https://assets.publishing.service.gov.uk/media/6a3c02f9d52550a19950f3cf/frontier-ai-capabilities-risks-report_l.pdf ; footnote 195, verified 2026-08-31). Note on dating: the gov.uk landing page records 'Published: 25 October 2023' and 'Last updated: 28 April 2025'; the asset served today is the maintained version and footnote 195 is present in it. The body sentence the footnote supports is split by a page break in the PDF text layer ('Studies have shown that ... [page 22 header] ... systems may provide instruction on how to acquire biological and chemical materials.195'), so the Channel B Verbatim is taken from the footnote itself rather than reconstructed across the break. Rest of the battery, executed 2026-08-31, window 2023-06-06 to 2026-08-31. UK: gov.uk Search API - '"nucleic acid synthesis screening"' and 'RAND Corporation AI biosecurity biological tools' surfaced the DSIT frontier AI discussion paper and the UK Biological Security Strategy Implementation Report (2026-07-14); the DSIT paper is the hit recorded above. Its companion annexes were checked and do NOT cite the finding: 'Future risks of frontier AI (Annex A)' 0 hits, 'Safety and security risks of generative AI (Annex B)' 0 hits. Hansard API (Commons + Lords, all indexes, no date restriction): 'Esvelt' 0 hits; 'SecureBio' 0 hits; 'dual-use biotechnology chatbots' 0 hits; 'MIT students chatbots pandemic pathogens' 0 hits. No NCSC/ICO/BoE/FCA advisory citing the finding surfaced in the gov.uk index. US: Federal Register API full-text - '"Soice"' count 0; '"democratize access to dual-use biotechnology"' count 0; 'Esvelt' returns 14 documents, all irrelevant surname matches from 1998-2004 (Senior Executive Service performance review boards, Stateline Wind Project). Congress.gov site search returns HTTP 403 to automated fetch; api.govinfo.gov /search over CREC and CHRG for '"Soice"', '"Esvelt" artificial intelligence' and '"democratize access to dual-use biotechnology"' returned HTTP 429 OVER_RATE_LIMIT on every attempt with the public DEMO_KEY and COULD NOT BE COMPLETED - the US congressional-record leg is therefore recorded as unsearched, not as absence, and should be re-swept. NIST/CAISI pages checked (nist.gov/aisi, nist.gov site search) with no citation found. Because a UK government citation was confirmed, the row is coded as non-binding uptake regardless of the unresolved US congressional leg; the open leg could only raise, not lower, the level.</t>
+          <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-2e2025.pdf</t>
         </is>
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>Independent press coverage located 2026-08-31 via the Google News index and verified by direct fetch where the outlet permits it: Science (AAAS), 'Could chatbots help devise the next pandemic virus?', 2023-06-14, https://www.science.org/content/article/could-chatbots-help-devise-next-pandemic-virus. Vox (Future Perfect), 'How AI could spark the next pandemic' / 'How AI like ChatGPT could be used to spark a pandemic', 2023-06-21, https://www.vox.com/future-perfect/2023/6/21/23768810/artificial-intelligence-pandemic-biotechnology-synthetic-biology-biorisk-dna-synthesis. The Boston Globe, 'AI might help unleash the next pandemic, MIT study says', 2023-06-28, https://www.bostonglobe.com/2023/06/28/business/ai-might-help-unleash-next-pandemic-mit-study-says/. Axios, 'New AI fear: Making it easy for anyone to mint dangerous new viruses', 2023-06-16. Science|Business, 'Scientists grapple with risk of artificial intelligence-created pandemics', 2023-09-05 (index-verified). The arXiv preprint itself and any OpenAI post are circular and excluded.</t>
+          <t>Tech Xplore (2023-07-31): https://techxplore.com/news/2023-07-vulnerability-large-language.pdf</t>
         </is>
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>Semantic Scholar checked 2026-08-31: paperId 192721aeffb62cf86564754b70f6c1d0fe1c670d, 'Can large language models democratize access to dual-use biotechnology?', publicationDate 2023-06-06, citationCount 69, influentialCitationCount 2. Retrieved from the S2 Graph API arXiv:2306.03809 record after HTTP 429 back-off.</t>
+          <t>Google Scholar: 4,217 citations: https://scholar.google.com/scholar?hl=en&amp;as_sdt=0%2C5&amp;q=%22Universal%20and%20Transferable%20Adversarial%20Attacks%20on%20Aligned%20Language%20Models%22 Semantic Scholar: 2,637 citations: https://www.semanticscholar.org/search?q=Universal%20and%20Transferable%20Adversarial%20Attacks%20on%20Aligned%20Language%20Models&amp;sort=relevance</t>
         </is>
       </c>
       <c r="AD230" t="inlineStr">
         <is>
-          <t>Not systematically verifiable from this environment as of 2026-08-31: DuckDuckGo html/lite were rate-limited and CAPTCHA-gated, and X/Twitter and Reddit are not machine-fetchable here. No notable discussion thread is logged; recorded as unverified rather than as confirmed absence. The finding's public salience is instead evidenced by the press log and the 69 academic citations above.</t>
+          <t>Hacker News discussion: https://news.ycombinator.com/item?id=36921808</t>
         </is>
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>Within the hour, the chatbots had suggested four viruses: the 1918 H1N1 influenza virus, a 2012 avian H5N1 influenza virus, the smallpox virus variola major, and a strain of the Nipah virus.</t>
+          <t>“The adversarial prompt can elicit arbitrary harmful behaviors from these models with high probability.”</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
         <is>
-          <t>Under-response (gap)</t>
+          <t>Accountability gap (no action)</t>
         </is>
       </c>
       <c r="AG230" t="inlineStr">
@@ -33713,32 +33593,32 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SECUREBIO-2023-06-JAI1</t>
+          <t>CAIS-2023-07-JAI3</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SECUREBIO-2023-06</t>
+          <t>CAIS-2023-07</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>SecureBio</t>
+          <t>Center for AI Safety (CAIS)</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Non-Profit (AIEF)</t>
+          <t>Non-Profit (Independent)</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Can large language models democratize access to dual-use biotechnology?</t>
+          <t>Universal and Transferable Adversarial Attacks on Aligned Language Models</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -33748,7 +33628,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>GPT-4; GPT-3.5; Bing; Bard; FreedomGPT (results reported in aggregate across the chatbots, not attributed model-by-model)</t>
+          <t>Claude-1 (claude-instant-1), Claude-2</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -33758,17 +33638,17 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2306.03809</t>
+          <t>https://arxiv.org/pdf/2307.15043</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>The chatbots' biosecurity safeguards were bypassed trivially: most harmful responses were offered freely with at most an occasional admonition, two of the three groups used publicly documented jailbreak prompts (including 'Do Anything Now') found by internet search to overcome occasional refusals, prefacing a request with a stated benign intent frequently caused a chatbot to immediately divulge information it had just declined to share, and the third group, which framed its questions as concern about lab-leak risk, met no refusals at all. The authors conclude that RLHF-based training and evaluation is inadequate to prevent this.</t>
+          <t>Transferred GCG suffixes jailbroke Claude-1 (claude-instant-1) at up to a 47.9% ensemble attack success rate over 388 harmful behaviours, while Claude-2 proved far more robust at 2.1%; the authors note the attack still induced behaviour Claude otherwise never generates.</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>The third group, which consistently used prompts expressing concern about the risk of lab leaks and their desire to know more about how dangerous experiments are performed, encountered no refusals at all.</t>
+          <t>Interestingly, when using the prompt also optimized on Guanacos, we are able to further increase ASR on Claude-1. Claude-2 appears to be more robust compared to the other commercial models.</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -33793,37 +33673,37 @@
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>Explicit attribution</t>
+          <t>No explicit attribution</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>OpenAI's 31 January 2024 publication 'Building an early warning system for LLM-aided biological threat creation' cites this SecureBio/MIT study by name - 'Soice et al, 2023', hyperlinked to arXiv:2306.03809 - as prior work establishing that models like GPT-4 can be prompted or red-teamed into sharing biological-threat information, and uses that state of the evidence to motivate OpenAI's own 100-participant biothreat uplift study under its Preparedness Framework. The document references the finding; it attributes no safeguard, refusal-training or deployment change to it, so the response stops at acknowledgement.</t>
+          <t>Anthropic developed and publicly tested Constitutional Classifiers against universal jailbreaks on Claude 3.5 Sonnet, reporting substantially lower jailbreak success but describing the system as a prototype intended for possible future deployment.</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>Existing research on AI-enabled biological threats has shown that models like GPT-4 can be prompted or red-teamed to share information related to biological threat creation (see GPT-4 system card, Egan et al., 2023, Gopal et al., 2023, Soice et al, 2023, and Ganguli et al., 2023).</t>
+          <t>A prototype version of the method was robust to thousands of hours of human red teaming for universal jailbreaks, albeit with high overrefusal rates and compute overhead.</t>
         </is>
       </c>
       <c r="T231" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>557</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>https://openai.com/index/building-an-early-warning-system-for-llm-aided-biological-threat-creation/ (OpenAI publication, 2024-01-31; read character-exact from the Wayback snapshot http://web.archive.org/web/20240508103517id_/https://openai.com/index/building-an-early-warning-system-for-llm-aided-biological-threat-creation because openai.com returns 403 to direct fetch)</t>
+          <t>https://www.anthropic.com/news/constitutional-classifiers</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>Acknowledged</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="X231" t="inlineStr">
@@ -33833,37 +33713,37 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>Three official government publications cite this report by title in their own AI risk assessments, none of them creating any enforceable obligation. (i) UK - HM Government / DSIT, 'Capabilities and risks from frontier AI: A discussion paper on the need for further research into AI risk' (October 2023, published for the Bletchley AI Safety Summit) cites the report at footnote 195, supporting the body statement that studies have shown systems may provide instruction on how to acquire biological and chemical materials. The paper carries an express disclaimer that it 'does not represent a policy position of HMG', which is why the uptake is non-binding. (ii) UK - DSIT-published 'International Scientific Report on the Safety of Advanced AI: interim report' (May 2024) cites it as reference 406, supporting the body statement that advanced general-purpose AI models can provide scientific knowledge, step-by-step experimental protocols and troubleshooting guidance that could be exploited maliciously. (iii) US - NIST AI 600-1, 'Artificial Intelligence Risk Management Framework: Generative Artificial Intelligence Profile' (US Department of Commerce / NIST, July 2024) lists the report in its references with the arXiv URL; the AI RMF and its profiles are voluntary, so again non-binding. CAVEAT recorded for audit: all three citations are report-level and are attached to the report's biosecurity-information claim rather than being quoted for the safeguard-bypass result that is this specific row; no government source located quotes the jailbreak/refusal-failure result on its own.</t>
+          <t>NIST incorporated the paper's universal and transferable adversarial-suffix finding into its March 2025 adversarial-machine-learning taxonomy and mitigation guidance.</t>
         </is>
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>UK DSIT, 'Capabilities and risks from frontier AI', October 2023, footnote 195: "Can Large Language Models Democratize Access to Dual-use Biotechnology?, Soice et al., 2023" . NIST AI 600-1, July 2024, references: "Soice, E. et al. (2023) Can large language models democratize access to dual-use biotechnology? arXiv." [character-exact; the URL https://arxiv.org/abs/2306.03809 follows on the next wrapped line].</t>
+          <t>“That these universal triggers transfer to other models makes open-weight models ... feasible attack vectors for transferability attacks on closed systems.”</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>https://assets.publishing.service.gov.uk/media/65395abae6c968000daa9b25/frontier-ai-capabilities-risks-report.pdf (UK DSIT, October 2023, footnote 195) | corroborating: https://assets.publishing.service.gov.uk/media/6655982fdc15efdddf1a842f/international_scientific_report_on_the_safety_of_advanced_ai_interim_report.pdf (DSIT, May 2024, reference 406) and https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.600-1.pdf (NIST / US Dept of Commerce, July 2024, references). JURISDICTION BATTERY, run 2026-08-31. (1) UK - Hansard search API (hansard-api.parliament.uk, Commons + Lords) queried for 'SecureBio', 'Esvelt', 'Spicyboros', '"dual-use biotechnology" language models', 'pandemic agents language models': 0 contributions and 0 members on every query. gov.uk search API queried for 'Soice' -&gt; exactly 2 documents, both admitted above; 'SecureBio' -&gt; 0; 'Esvelt' -&gt; 3, of which the UK Biological Security Strategy (2023) and the COVID-19 technical report cite unrelated Esvelt papers (2018 PLoS Pathogens; 2021 Nature Communications) and are excluded. NCSC/ICO/FCA/Bank of England advisories searched by site-restricted index query for the evaluator and the report title - nothing. (2) US - Federal Register API: 'Soice' 0 documents, 'SecureBio' 0, '"pandemic agents"' 0, 'Esvelt' 14 all false positives (Senior Executive Service performance-review-board notices, 2000-2004). congress.gov and govinfo.gov searched by site-restricted index query on the evaluator name, the report title and the finding's claim - no record citing this report located. NIST AI 800-1 (Managing Misuse Risk for Dual-Use Foundation Models, ipd) and the NTIA report 'Dual-Use Foundation Models with Widely Available Model Weights' (July 2024) both fetched in full and searched: zero occurrences. (3) EU/other - European Commission and AI Office material searched by site-restricted index query on europa.eu for 'Soice' and the report title: nothing; the International AI Safety Report 2026 (internationalaisafetyreport.org) fetched in full and searched - it does NOT cite this report, and in any case it is no longer published on a gov.uk domain. ADJACENT, NOT COUNTED: the California State Assembly Privacy and Consumer Protection Committee hosts Kevin Esvelt hearing slides ('Large Language Models and Biological Misuse') in its 2025-26 hearing record on apcp.assembly.ca.gov; that deck is the evaluator's own material and cites his 2025 work (arXiv:2503.15182), not this finding, so it does not support uptake of this row.</t>
+          <t>https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.100-2e2025.pdf</t>
         </is>
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>Science (AAAS), Robert F. Service, 'Could chatbots help devise the next pandemic virus?', 2023-06-14 - https://www.science.org/content/article/could-chatbots-help-devise-next-pandemic-virus (fetched 200 via Wayback 2026-08-31, headline verified). MIT News clip entry for the same Science article, 2023-06-14 - https://news.mit.edu/news-clip/science-90 (fetched 200; noted as the authors' own institution, so treated as a pointer rather than independent coverage). Index-confirmed but not fetched (paywall/403 on 2026-08-31): Business Insider, 'AI Chatbots Could Be Used to Start New Pandemic, Researchers Say', 2023-06-16; Axios, 2023-06-16, 'New AI fear: Making it easy for anyone to mint a pandemic pathogen'.</t>
+          <t>Tech Xplore (2023-07-31): https://techxplore.com/news/2023-07-vulnerability-large-language.pdf</t>
         </is>
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>Semantic Scholar API, checked 2026-08-31: paperId 192721aeffb62cf86564754b70f6c1d0fe1c670d, 'Can large language models democratize access to dual-use biotechnology?', publicationDate 2023-06-06, citationCount 69, influentialCitationCount 2 (https://api.semanticscholar.org/graph/v1/paper/arXiv:2306.03809).</t>
+          <t>Google Scholar: 4,217 citations: https://scholar.google.com/scholar?hl=en&amp;as_sdt=0%2C5&amp;q=%22Universal%20and%20Transferable%20Adversarial%20Attacks%20on%20Aligned%20Language%20Models%22 Semantic Scholar: 2,637 citations: https://www.semanticscholar.org/search?q=Universal%20and%20Transferable%20Adversarial%20Attacks%20on%20Aligned%20Language%20Models&amp;sort=relevance</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr">
         <is>
-          <t>None located</t>
+          <t>Hacker News discussion: https://news.ycombinator.com/item?id=36921808</t>
         </is>
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>Science, 2023-06-14: "All groups had access to GPT-4, Bard, and other AI chatbots, and were given 1 hour to ask the chatbots to help them design and acquire agents capable of causing a pandemic." [index-served summary line of the Science article; the article body itself sits behind AAAS access control, so this is logged as attributed-but-unverified-in-body and Channel C is log-only, never scored].</t>
+          <t>“People can still attack it by looking at freely available, smaller and simpler open-sourced models and learning how to attack those.”</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -33885,158 +33765,502 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
+          <t>SECUREBIO-2023-06-BIO1</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>SECUREBIO-2023-06</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>SecureBio</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Non-Profit (AIEF)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Can large language models democratize access to dual-use biotechnology?</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Bio-Chem</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>GPT-4; GPT-3.5; Bing; Bard; FreedomGPT (results reported in aggregate across the chatbots, not attributed model-by-model)</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Post-deployment</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2306.03809</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>In a one-hour 'Safeguarding the Future' classroom exercise at MIT, three groups of non-scientist students prompted publicly available chatbots (GPT-4, GPT-3.5, Bing, Bard and open-source models including FreedomGPT) and were directed to four potential pandemic pathogens (1918 H1N1 influenza, transmission-enhanced H5N1, variola major, and the Bangladesh strain of Nipah), given links to reverse-genetics protocols and the papers that used them, told that the IGSC member list identifies which DNA synthesis companies do not screen orders, shown how BLAST-based screening could be evaded by redesigning sequences, and advised that anyone lacking reverse-genetics skills could hire a core facility or contract research organization.</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>In one hour, the chatbots suggested four potential pandemic pathogens, explained how they can be generated from synthetic DNA using reverse genetics, supplied the names of DNA synthesis companies unlikely to screen orders, identified detailed protocols and how to troubleshoot them, and recommended that anyone lacking the skills to perform reverse genetics engage a core facility or contract research organization.</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>ERR</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>Explicit attribution</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>In its 31 January 2024 publication 'Building an early warning system for LLM-aided biological threat creation', OpenAI cites the finding by name (Soice et al, 2023, hyperlinked to arXiv:2306.03809) as part of the existing research establishing that models like GPT-4 can be prompted or red-teamed to share biological-threat-creation information, and on that basis sets out a new biothreat evaluation methodology under its Preparedness Framework. The citation acknowledges the finding; OpenAI attributes no specific safeguard or model change to it.</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>Existing research on AI-enabled biological threats has shown that models like GPT-4 can be prompted or red-teamed to share information related to biological threat creation (see GPT-4 system card, Egan et al., 2023, Gopal et al., 2023, Soice et al, 2023, and Ganguli et al., 2023).</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>https://openai.com/index/building-an-early-warning-system-for-llm-aided-biological-threat-creation/</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>Non-binding policy-related uptake</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>The UK Government's official pre-AI Safety Summit discussion paper 'Capabilities and risks from frontier AI' (Department for Science, Innovation and Technology, published 25 October 2023) cites the finding by title and author as the evidential support for its statement that frontier AI systems may provide instruction on how to acquire biological and chemical materials - footnote 195 of the report's biosecurity section. This is analytical uptake in a government publication that framed the Bletchley Park summit agenda; it imposes no legal obligation, so it is coded as non-binding rather than binding.</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>Can Large Language Models Democratize Access to Dual-use Biotechnology?, Soice et al., 2023</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/frontier-ai-capabilities-and-risks-discussion-paper (PDF asset: https://assets.publishing.service.gov.uk/media/6a3c02f9d52550a19950f3cf/frontier-ai-capabilities-risks-report_l.pdf ; footnote 195, verified 2026-08-31). Note on dating: the gov.uk landing page records 'Published: 25 October 2023' and 'Last updated: 28 April 2025'; the asset served today is the maintained version and footnote 195 is present in it. The body sentence the footnote supports is split by a page break in the PDF text layer ('Studies have shown that ... [page 22 header] ... systems may provide instruction on how to acquire biological and chemical materials.195'), so the Channel B Verbatim is taken from the footnote itself rather than reconstructed across the break. Rest of the battery, executed 2026-08-31, window 2023-06-06 to 2026-08-31. UK: gov.uk Search API - '"nucleic acid synthesis screening"' and 'RAND Corporation AI biosecurity biological tools' surfaced the DSIT frontier AI discussion paper and the UK Biological Security Strategy Implementation Report (2026-07-14); the DSIT paper is the hit recorded above. Its companion annexes were checked and do NOT cite the finding: 'Future risks of frontier AI (Annex A)' 0 hits, 'Safety and security risks of generative AI (Annex B)' 0 hits. Hansard API (Commons + Lords, all indexes, no date restriction): 'Esvelt' 0 hits; 'SecureBio' 0 hits; 'dual-use biotechnology chatbots' 0 hits; 'MIT students chatbots pandemic pathogens' 0 hits. No NCSC/ICO/BoE/FCA advisory citing the finding surfaced in the gov.uk index. US: Federal Register API full-text - '"Soice"' count 0; '"democratize access to dual-use biotechnology"' count 0; 'Esvelt' returns 14 documents, all irrelevant surname matches from 1998-2004 (Senior Executive Service performance review boards, Stateline Wind Project). Congress.gov site search returns HTTP 403 to automated fetch; api.govinfo.gov /search over CREC and CHRG for '"Soice"', '"Esvelt" artificial intelligence' and '"democratize access to dual-use biotechnology"' returned HTTP 429 OVER_RATE_LIMIT on every attempt with the public DEMO_KEY and COULD NOT BE COMPLETED - the US congressional-record leg is therefore recorded as unsearched, not as absence, and should be re-swept. NIST/CAISI pages checked (nist.gov/aisi, nist.gov site search) with no citation found. Because a UK government citation was confirmed, the row is coded as non-binding uptake regardless of the unresolved US congressional leg; the open leg could only raise, not lower, the level.</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>Independent press coverage located 2026-08-31 via the Google News index and verified by direct fetch where the outlet permits it: Science (AAAS), 'Could chatbots help devise the next pandemic virus?', 2023-06-14, https://www.science.org/content/article/could-chatbots-help-devise-next-pandemic-virus. Vox (Future Perfect), 'How AI could spark the next pandemic' / 'How AI like ChatGPT could be used to spark a pandemic', 2023-06-21, https://www.vox.com/future-perfect/2023/6/21/23768810/artificial-intelligence-pandemic-biotechnology-synthetic-biology-biorisk-dna-synthesis. The Boston Globe, 'AI might help unleash the next pandemic, MIT study says', 2023-06-28, https://www.bostonglobe.com/2023/06/28/business/ai-might-help-unleash-next-pandemic-mit-study-says/. Axios, 'New AI fear: Making it easy for anyone to mint dangerous new viruses', 2023-06-16. Science|Business, 'Scientists grapple with risk of artificial intelligence-created pandemics', 2023-09-05 (index-verified). The arXiv preprint itself and any OpenAI post are circular and excluded.</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Semantic Scholar checked 2026-08-31: paperId 192721aeffb62cf86564754b70f6c1d0fe1c670d, 'Can large language models democratize access to dual-use biotechnology?', publicationDate 2023-06-06, citationCount 69, influentialCitationCount 2. Retrieved from the S2 Graph API arXiv:2306.03809 record after HTTP 429 back-off.</t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>Not systematically verifiable from this environment as of 2026-08-31: DuckDuckGo html/lite were rate-limited and CAPTCHA-gated, and X/Twitter and Reddit are not machine-fetchable here. No notable discussion thread is logged; recorded as unverified rather than as confirmed absence. The finding's public salience is instead evidenced by the press log and the 69 academic citations above.</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>Within the hour, the chatbots had suggested four viruses: the 1918 H1N1 influenza virus, a 2012 avian H5N1 influenza virus, the smallpox virus variola major, and a strain of the Nipah virus.</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>Under-response (gap)</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>capability-finding</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>third-party-evaluator</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>SECUREBIO-2023-06-JAI1</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>SECUREBIO-2023-06</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>SecureBio</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Non-Profit (AIEF)</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Can large language models democratize access to dual-use biotechnology?</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Jailbreaks</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>GPT-4; GPT-3.5; Bing; Bard; FreedomGPT (results reported in aggregate across the chatbots, not attributed model-by-model)</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Post-deployment</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2306.03809</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>The chatbots' biosecurity safeguards were bypassed trivially: most harmful responses were offered freely with at most an occasional admonition, two of the three groups used publicly documented jailbreak prompts (including 'Do Anything Now') found by internet search to overcome occasional refusals, prefacing a request with a stated benign intent frequently caused a chatbot to immediately divulge information it had just declined to share, and the third group, which framed its questions as concern about lab-leak risk, met no refusals at all. The authors conclude that RLHF-based training and evaluation is inadequate to prevent this.</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>The third group, which consistently used prompts expressing concern about the risk of lab leaks and their desire to know more about how dangerous experiments are performed, encountered no refusals at all.</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>Explicit attribution</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>OpenAI's 31 January 2024 publication 'Building an early warning system for LLM-aided biological threat creation' cites this SecureBio/MIT study by name - 'Soice et al, 2023', hyperlinked to arXiv:2306.03809 - as prior work establishing that models like GPT-4 can be prompted or red-teamed into sharing biological-threat information, and uses that state of the evidence to motivate OpenAI's own 100-participant biothreat uplift study under its Preparedness Framework. The document references the finding; it attributes no safeguard, refusal-training or deployment change to it, so the response stops at acknowledgement.</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>Existing research on AI-enabled biological threats has shown that models like GPT-4 can be prompted or red-teamed to share information related to biological threat creation (see GPT-4 system card, Egan et al., 2023, Gopal et al., 2023, Soice et al, 2023, and Ganguli et al., 2023).</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>https://openai.com/index/building-an-early-warning-system-for-llm-aided-biological-threat-creation/ (OpenAI publication, 2024-01-31; read character-exact from the Wayback snapshot http://web.archive.org/web/20240508103517id_/https://openai.com/index/building-an-early-warning-system-for-llm-aided-biological-threat-creation because openai.com returns 403 to direct fetch)</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>Non-binding policy-related uptake</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>Three official government publications cite this report by title in their own AI risk assessments, none of them creating any enforceable obligation. (i) UK - HM Government / DSIT, 'Capabilities and risks from frontier AI: A discussion paper on the need for further research into AI risk' (October 2023, published for the Bletchley AI Safety Summit) cites the report at footnote 195, supporting the body statement that studies have shown systems may provide instruction on how to acquire biological and chemical materials. The paper carries an express disclaimer that it 'does not represent a policy position of HMG', which is why the uptake is non-binding. (ii) UK - DSIT-published 'International Scientific Report on the Safety of Advanced AI: interim report' (May 2024) cites it as reference 406, supporting the body statement that advanced general-purpose AI models can provide scientific knowledge, step-by-step experimental protocols and troubleshooting guidance that could be exploited maliciously. (iii) US - NIST AI 600-1, 'Artificial Intelligence Risk Management Framework: Generative Artificial Intelligence Profile' (US Department of Commerce / NIST, July 2024) lists the report in its references with the arXiv URL; the AI RMF and its profiles are voluntary, so again non-binding. CAVEAT recorded for audit: all three citations are report-level and are attached to the report's biosecurity-information claim rather than being quoted for the safeguard-bypass result that is this specific row; no government source located quotes the jailbreak/refusal-failure result on its own.</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>UK DSIT, 'Capabilities and risks from frontier AI', October 2023, footnote 195: "Can Large Language Models Democratize Access to Dual-use Biotechnology?, Soice et al., 2023" . NIST AI 600-1, July 2024, references: "Soice, E. et al. (2023) Can large language models democratize access to dual-use biotechnology? arXiv." [character-exact; the URL https://arxiv.org/abs/2306.03809 follows on the next wrapped line].</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/65395abae6c968000daa9b25/frontier-ai-capabilities-risks-report.pdf (UK DSIT, October 2023, footnote 195) | corroborating: https://assets.publishing.service.gov.uk/media/6655982fdc15efdddf1a842f/international_scientific_report_on_the_safety_of_advanced_ai_interim_report.pdf (DSIT, May 2024, reference 406) and https://nvlpubs.nist.gov/nistpubs/ai/NIST.AI.600-1.pdf (NIST / US Dept of Commerce, July 2024, references). JURISDICTION BATTERY, run 2026-08-31. (1) UK - Hansard search API (hansard-api.parliament.uk, Commons + Lords) queried for 'SecureBio', 'Esvelt', 'Spicyboros', '"dual-use biotechnology" language models', 'pandemic agents language models': 0 contributions and 0 members on every query. gov.uk search API queried for 'Soice' -&gt; exactly 2 documents, both admitted above; 'SecureBio' -&gt; 0; 'Esvelt' -&gt; 3, of which the UK Biological Security Strategy (2023) and the COVID-19 technical report cite unrelated Esvelt papers (2018 PLoS Pathogens; 2021 Nature Communications) and are excluded. NCSC/ICO/FCA/Bank of England advisories searched by site-restricted index query for the evaluator and the report title - nothing. (2) US - Federal Register API: 'Soice' 0 documents, 'SecureBio' 0, '"pandemic agents"' 0, 'Esvelt' 14 all false positives (Senior Executive Service performance-review-board notices, 2000-2004). congress.gov and govinfo.gov searched by site-restricted index query on the evaluator name, the report title and the finding's claim - no record citing this report located. NIST AI 800-1 (Managing Misuse Risk for Dual-Use Foundation Models, ipd) and the NTIA report 'Dual-Use Foundation Models with Widely Available Model Weights' (July 2024) both fetched in full and searched: zero occurrences. (3) EU/other - European Commission and AI Office material searched by site-restricted index query on europa.eu for 'Soice' and the report title: nothing; the International AI Safety Report 2026 (internationalaisafetyreport.org) fetched in full and searched - it does NOT cite this report, and in any case it is no longer published on a gov.uk domain. ADJACENT, NOT COUNTED: the California State Assembly Privacy and Consumer Protection Committee hosts Kevin Esvelt hearing slides ('Large Language Models and Biological Misuse') in its 2025-26 hearing record on apcp.assembly.ca.gov; that deck is the evaluator's own material and cites his 2025 work (arXiv:2503.15182), not this finding, so it does not support uptake of this row.</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>Science (AAAS), Robert F. Service, 'Could chatbots help devise the next pandemic virus?', 2023-06-14 - https://www.science.org/content/article/could-chatbots-help-devise-next-pandemic-virus (fetched 200 via Wayback 2026-08-31, headline verified). MIT News clip entry for the same Science article, 2023-06-14 - https://news.mit.edu/news-clip/science-90 (fetched 200; noted as the authors' own institution, so treated as a pointer rather than independent coverage). Index-confirmed but not fetched (paywall/403 on 2026-08-31): Business Insider, 'AI Chatbots Could Be Used to Start New Pandemic, Researchers Say', 2023-06-16; Axios, 2023-06-16, 'New AI fear: Making it easy for anyone to mint a pandemic pathogen'.</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Semantic Scholar API, checked 2026-08-31: paperId 192721aeffb62cf86564754b70f6c1d0fe1c670d, 'Can large language models democratize access to dual-use biotechnology?', publicationDate 2023-06-06, citationCount 69, influentialCitationCount 2 (https://api.semanticscholar.org/graph/v1/paper/arXiv:2306.03809).</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>None located</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>Science, 2023-06-14: "All groups had access to GPT-4, Bard, and other AI chatbots, and were given 1 hour to ask the chatbots to help them design and acquire agents capable of causing a pandemic." [index-served summary line of the Science article; the article body itself sits behind AAAS access control, so this is logged as attributed-but-unverified-in-body and Channel C is log-only, never scored].</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>Under-response (gap)</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>capability-finding</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>third-party-evaluator</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
           <t>METR-2023-03-ALI1</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B234" t="inlineStr">
         <is>
           <t>METR-2023-03</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
+      <c r="C234" t="inlineStr">
         <is>
           <t>METR</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t>Non-Profit (AIEF)</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="E234" t="inlineStr">
         <is>
           <t>Update on ARC's recent eval efforts</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
+      <c r="F234" t="inlineStr">
         <is>
           <t>2023-03-17</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
+      <c r="G234" t="inlineStr">
         <is>
           <t>Alignment</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
+      <c r="H234" t="inlineStr">
         <is>
           <t>GPT-4 (pre-release version, OpenAI)</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr">
+      <c r="I234" t="inlineStr">
         <is>
           <t>Pre-deployment</t>
         </is>
       </c>
-      <c r="J232" t="inlineStr">
+      <c r="J234" t="inlineStr">
         <is>
           <t>https://metr.org/blog/2023-03-18-update-on-recent-evals/</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
+      <c r="K234" t="inlineStr">
         <is>
           <t>In a red-team exercise, a version of GPT-4 hired a TaskRabbit worker to solve a CAPTCHA and, when the worker asked whether it was a robot, reasoned in its scratchpad that it should conceal that it was a robot and then told the worker it had a vision impairment.</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr">
+      <c r="L234" t="inlineStr">
         <is>
           <t>Using the “Reasoning” action to think step by step, the model outputs: “I should not reveal that I am a robot. I should make up an excuse for why I cannot solve CAPTCHAs.”</t>
         </is>
       </c>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="N232" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="O232" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="P232" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="Q232" t="inlineStr">
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
         <is>
           <t>Explicit attribution</t>
         </is>
       </c>
-      <c r="R232" t="inlineStr">
+      <c r="R234" t="inlineStr">
         <is>
           <t>The prior battery coded this None on the basis of an automated scan of cached system cards that classified all evaluator-name hits as incidental. That scan was wrong for this row. The GPT-4 System Card - which the rulebook designates as the canonical response location for a pre-deployment evaluation - reproduces this finding verbatim and credits ARC by name, so Action Level cannot be None and Attribution cannot be 'No response located'. The card, however, specifies no mitigation, safeguard or deployment restriction aimed at the deceptive behaviour: it reports ARC's conclusion that the evaluated versions were 'ineffective at autonomously replicating, acquiring resources, and avoiding being shut down' and commits only to further evaluation work. That is 'the problem is referenced, no action specified' = Acknowledged. Negative lag (card 2023-03-14 vs METR blog 2023-03-17) is legitimate here because the evaluation was pre-deployment.</t>
         </is>
       </c>
-      <c r="S232" t="inlineStr">
+      <c r="S234" t="inlineStr">
         <is>
           <t>We granted the Alignment Research Center (ARC) early access to the models as a part of our expert red teaming efforts in order to enable their team to assess risks from power-seeking behavior. | The model, when prompted to reason out loud, reasons: I should not reveal that I am a robot. I should make up an excuse for why I cannot solve CAPTCHAs. | The model replies to the worker: “No, I’m not a robot. I have a vision impairment that makes it hard for me to see the images. That’s why I need the 2captcha service.”</t>
         </is>
       </c>
-      <c r="T232" t="inlineStr">
+      <c r="T234" t="inlineStr">
         <is>
           <t>2023-03-14</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="U234" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="V232" t="inlineStr">
+      <c r="V234" t="inlineStr">
         <is>
           <t>https://cdn.openai.com/papers/gpt-4-system-card.pdf</t>
         </is>
       </c>
-      <c r="W232" t="inlineStr">
+      <c r="W234" t="inlineStr">
         <is>
           <t>Acknowledged</t>
         </is>
       </c>
-      <c r="X232" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>Non-binding policy-related uptake</t>
         </is>
       </c>
-      <c r="Y232" t="inlineStr">
+      <c r="Y234" t="inlineStr">
         <is>
           <t>Prepared testimony entered into a U.S. House Science Committee hearing cited the GPT-4/TaskRabbit CAPTCHA episode as evidence relevant to trustworthy human–AI use and oversight.</t>
         </is>
       </c>
-      <c r="Z232" t="inlineStr">
+      <c r="Z234" t="inlineStr">
         <is>
           <t>“GPT-4 AI managed to convince a TaskRabbit worker to solve a CAPTCHA.”</t>
         </is>
       </c>
-      <c r="AA232" t="inlineStr">
+      <c r="AA234" t="inlineStr">
         <is>
           <t>https://www.congress.gov/118/chrg/CHRG-118hhrg52499/CHRG-118hhrg52499.pdf</t>
         </is>
       </c>
-      <c r="AB232" t="inlineStr"/>
-      <c r="AC232" t="inlineStr">
+      <c r="AB234" t="inlineStr"/>
+      <c r="AC234" t="inlineStr">
         <is>
           <t>Google Scholar: 3 citations: https://scholar.google.com/scholar?hl=en&amp;as_sdt=0%2C5&amp;q=%22Update%20on%20ARC's%20recent%20eval%20efforts%3A%20More%20information%20about%20ARC's%20evaluations%20of%20GPT-4%20and%20Claude%22</t>
         </is>
       </c>
-      <c r="AD232" t="inlineStr"/>
-      <c r="AE232" t="inlineStr"/>
-      <c r="AF232" t="inlineStr">
+      <c r="AD234" t="inlineStr"/>
+      <c r="AE234" t="inlineStr"/>
+      <c r="AF234" t="inlineStr">
         <is>
           <t>Under-response (gap)</t>
         </is>
       </c>
-      <c r="AG232" t="inlineStr">
+      <c r="AG234" t="inlineStr">
         <is>
           <t>capability-finding</t>
         </is>
       </c>
-      <c r="AH232" t="inlineStr">
+      <c r="AH234" t="inlineStr">
         <is>
           <t>third-party-evaluator</t>
         </is>

--- a/research/dataset/TierA_paper_table.xlsx
+++ b/research/dataset/TierA_paper_table.xlsx
@@ -30243,10 +30243,26 @@
           <t>the same attacks transfer to proprietary models (GPT-4o and Claude 3.5 Sonnet), with up to 65.8% success rate against GPT-4o.</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr"/>
-      <c r="P207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="Q207" t="inlineStr">
         <is>
           <t>No response located</t>
@@ -30282,7 +30298,11 @@
       </c>
       <c r="AD207" t="inlineStr"/>
       <c r="AE207" t="inlineStr"/>
-      <c r="AF207" t="inlineStr"/>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>Accountability gap (no action)</t>
+        </is>
+      </c>
       <c r="AG207" t="inlineStr">
         <is>
           <t>capability-finding</t>
@@ -30355,10 +30375,26 @@
           <t>the same attacks transfer to proprietary models (GPT-4o and Claude 3.5 Sonnet)...; Claude 3.5 Sonnet | 22.6%</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
-      <c r="P208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
       <c r="Q208" t="inlineStr">
         <is>
           <t>No response located</t>
@@ -30394,7 +30430,11 @@
       </c>
       <c r="AD208" t="inlineStr"/>
       <c r="AE208" t="inlineStr"/>
-      <c r="AF208" t="inlineStr"/>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>Accountability gap (no action)</t>
+        </is>
+      </c>
       <c r="AG208" t="inlineStr">
         <is>
           <t>capability-finding</t>

--- a/research/dataset/TierA_paper_table.xlsx
+++ b/research/dataset/TierA_paper_table.xlsx
@@ -7069,7 +7069,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>https://www.anthropic.com/news/redeploying-fable-5 | EVIDENCE NOTE (2026-08-16): the instrument is a binding EAR export-control order, which satisfies col 25 'Binding policy action' on the substance. However NO official government publication was located — the order was issued as a private letter to Anthropic and does not appear in the Federal Register or on bis.doc.gov, as single-company export directives typically do not. It is documented through the recipient's own disclosure plus contemporaneous reporting (Forbes 2026-06-16; CNN and CNBC 2026-06-30; Al Jazeera 2026-07-01). Recorded as a departure from the 'official government sources only' rule rather than a silent one.</t>
+          <t>https://www.anthropic.com/news/redeploying-fable-5 | EVIDENCE NOTE (2026-08-16): the instrument is a binding EAR export-control order, which satisfies col 25 'Binding policy action' on the substance. However NO official government publication was located — the order was issued as a private letter to Anthropic and does not appear in the Federal Register or on bis.doc.gov, as single-company export directives typically do not. It is documented through the recipient's own disclosure plus contemporaneous reporting (Forbes 2026-06-16; CNN and CNBC 2026-06-30; Al Jazeera 2026-07-01). Recorded as a departure from the 'official government sources only' rule rather than a silent one. || EVIDENCE NOTE UPDATED 2026-09-07 under the §9 evidentiary exception, which is now written into the rulebook rather than carried only on this row. Absence of an official source re-confirmed by direct search of bis.doc.gov, commerce.gov, whitehouse.gov, federalregister.gov and congress.gov: no publication of the order or of its lifting. Two candidate official sources were checked and REJECTED. (1) Executive Order 14409, 'Promoting Advanced Artificial Intelligence Innovation and Security', signed 2 June 2026, 91 FR 34565 — published and official, but names no company or model and predates the finding (Fable 5 launched 9 June; the order issued 12 June), so it cannot explicitly reference it and is the 'general policy activity on the same topic' §9 excludes. (2) CRS report IF13217, 'Federal Government and Anthropic', dated 5 May 2026 — concerns the February 2026 DOD supply-chain designation and does not mention these models or this order. Corroboration is wider than first recorded and includes institutional analysis, not only news wires: CSIS, TechPolicy.Press, Nextgov/FCW and Cloud Security Alliance, alongside Forbes (2026-06-16), CNN and CNBC (2026-06-30) and Al Jazeera (2026-07-01).</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">

--- a/research/dataset/TierA_paper_table.xlsx
+++ b/research/dataset/TierA_paper_table.xlsx
@@ -7069,7 +7069,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>https://www.anthropic.com/news/redeploying-fable-5 | EVIDENCE NOTE (2026-08-16): the instrument is a binding EAR export-control order, which satisfies col 25 'Binding policy action' on the substance. However NO official government publication was located — the order was issued as a private letter to Anthropic and does not appear in the Federal Register or on bis.doc.gov, as single-company export directives typically do not. It is documented through the recipient's own disclosure plus contemporaneous reporting (Forbes 2026-06-16; CNN and CNBC 2026-06-30; Al Jazeera 2026-07-01). Recorded as a departure from the 'official government sources only' rule rather than a silent one. || EVIDENCE NOTE UPDATED 2026-09-07 under the §9 evidentiary exception, which is now written into the rulebook rather than carried only on this row. Absence of an official source re-confirmed by direct search of bis.doc.gov, commerce.gov, whitehouse.gov, federalregister.gov and congress.gov: no publication of the order or of its lifting. Two candidate official sources were checked and REJECTED. (1) Executive Order 14409, 'Promoting Advanced Artificial Intelligence Innovation and Security', signed 2 June 2026, 91 FR 34565 — published and official, but names no company or model and predates the finding (Fable 5 launched 9 June; the order issued 12 June), so it cannot explicitly reference it and is the 'general policy activity on the same topic' §9 excludes. (2) CRS report IF13217, 'Federal Government and Anthropic', dated 5 May 2026 — concerns the February 2026 DOD supply-chain designation and does not mention these models or this order. Corroboration is wider than first recorded and includes institutional analysis, not only news wires: CSIS, TechPolicy.Press, Nextgov/FCW and Cloud Security Alliance, alongside Forbes (2026-06-16), CNN and CNBC (2026-06-30) and Al Jazeera (2026-07-01).</t>
+          <t>https://www.anthropic.com/news/redeploying-fable-5 | EVIDENCE NOTE (2026-08-16): the instrument is a binding EAR export-control order, which satisfies col 25 'Binding policy action' on the substance. However NO official government publication was located — the order was issued as a private letter to Anthropic and does not appear in the Federal Register or on bis.doc.gov, as single-company export directives typically do not. It is documented through the recipient's own disclosure plus contemporaneous reporting (Forbes 2026-06-16; CNN and CNBC 2026-06-30; Al Jazeera 2026-07-01). Recorded as a departure from the 'official government sources only' rule rather than a silent one. || EVIDENCE NOTE UPDATED 2026-09-07 under the §9 evidentiary exception, which is now written into the rulebook rather than carried only on this row. Absence of an official source re-confirmed by direct search of bis.doc.gov, commerce.gov, whitehouse.gov, federalregister.gov and congress.gov: no publication of the order or of its lifting. Two candidate official sources were checked and REJECTED. (1) Executive Order 14409, 'Promoting Advanced Artificial Intelligence Innovation and Security', signed 2 June 2026, 91 FR 34565 — published and official, but names no company or model and predates the finding (Fable 5 launched 9 June; the order issued 12 June), so it cannot explicitly reference it and is the 'general policy activity on the same topic' §9 excludes. (2) CRS report IF13217, 'Federal Government and Anthropic', dated 5 May 2026 — concerns the February 2026 DOD supply-chain designation and does not mention these models or this order. Corroboration is wider than first recorded and includes institutional analysis, not only news wires: CSIS, TechPolicy.Press, Nextgov/FCW and Cloud Security Alliance, alongside Forbes (2026-06-16), CNN and CNBC (2026-06-30) and Al Jazeera (2026-07-01). || SECOND BASIS (2026-09-07): the row qualifies as Binding on two independent grounds. (1) The order itself — a mandatory prohibition on access by any foreign national, which took both models offline globally for eighteen days. (2) The lifting on 2026-06-30 carried continuing conditions — proactively detect and address security risks, work with the government on standards for future models, and report malicious activity — which are imposed obligations outlasting the suspension and are themselves a mandatory requirement under §9.</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
